--- a/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B04_Normal_2.xlsx
+++ b/results/block2_results/area/Normal_2/branches/dataframes/dataset_LCA_B04_Normal_2.xlsx
@@ -523,7 +523,7 @@
         <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1865502853357017</v>
+        <v>0.1865600545781031</v>
       </c>
     </row>
     <row r="3">
@@ -564,7 +564,7 @@
         <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9027069616915873</v>
+        <v>0.9025130183448353</v>
       </c>
     </row>
     <row r="4">
@@ -605,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.329790079151363</v>
+        <v>1.329840539349983</v>
       </c>
     </row>
     <row r="5">
@@ -646,7 +646,7 @@
         <v>5</v>
       </c>
       <c r="K5" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="6">
@@ -687,7 +687,7 @@
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>3.45343381859624</v>
+        <v>3.466416537272089</v>
       </c>
     </row>
     <row r="7">
@@ -728,7 +728,7 @@
         <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>5.333486823954726</v>
+        <v>5.331086360382172</v>
       </c>
     </row>
     <row r="8">
@@ -769,7 +769,7 @@
         <v>5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.042760034830393</v>
+        <v>6.039954809969425</v>
       </c>
     </row>
     <row r="9">
@@ -810,7 +810,7 @@
         <v>5</v>
       </c>
       <c r="K9" t="n">
-        <v>9.774211633003286</v>
+        <v>9.635797748144768</v>
       </c>
     </row>
     <row r="10">
@@ -851,7 +851,7 @@
         <v>5</v>
       </c>
       <c r="K10" t="n">
-        <v>10.47404150664014</v>
+        <v>10.47449632497913</v>
       </c>
     </row>
     <row r="11">
@@ -892,7 +892,7 @@
         <v>5</v>
       </c>
       <c r="K11" t="n">
-        <v>10.50943319366649</v>
+        <v>10.50475136658863</v>
       </c>
     </row>
     <row r="12">
@@ -933,7 +933,7 @@
         <v>5</v>
       </c>
       <c r="K12" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="13">
@@ -974,7 +974,7 @@
         <v>5</v>
       </c>
       <c r="K13" t="n">
-        <v>12.00213237476259</v>
+        <v>11.98254064055079</v>
       </c>
     </row>
     <row r="14">
@@ -1015,7 +1015,7 @@
         <v>5</v>
       </c>
       <c r="K14" t="n">
-        <v>12.33737930054762</v>
+        <v>12.33786735892068</v>
       </c>
     </row>
     <row r="15">
@@ -1056,7 +1056,7 @@
         <v>5</v>
       </c>
       <c r="K15" t="n">
-        <v>1.112358201660258</v>
+        <v>1.112431640076021</v>
       </c>
     </row>
     <row r="16">
@@ -1097,7 +1097,7 @@
         <v>5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.062777698332418</v>
+        <v>1.063099514135826</v>
       </c>
     </row>
     <row r="17">
@@ -1138,7 +1138,7 @@
         <v>5</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5772589909199825</v>
+        <v>0.5792498871576799</v>
       </c>
     </row>
     <row r="18">
@@ -1179,7 +1179,7 @@
         <v>5</v>
       </c>
       <c r="K18" t="n">
-        <v>15.92122532206255</v>
+        <v>16.08614487448754</v>
       </c>
     </row>
     <row r="19">
@@ -1220,7 +1220,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="n">
-        <v>15.92244207042752</v>
+        <v>15.9224055805709</v>
       </c>
     </row>
     <row r="20">
@@ -1261,7 +1261,7 @@
         <v>5</v>
       </c>
       <c r="K20" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1302,7 @@
         <v>5</v>
       </c>
       <c r="K21" t="n">
-        <v>15.90440478338968</v>
+        <v>15.90529663782263</v>
       </c>
     </row>
     <row r="22">
@@ -1343,7 +1343,7 @@
         <v>5</v>
       </c>
       <c r="K22" t="n">
-        <v>15.95062527901377</v>
+        <v>15.94907264007682</v>
       </c>
     </row>
     <row r="23">
@@ -1384,7 +1384,7 @@
         <v>5</v>
       </c>
       <c r="K23" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="24">
@@ -1425,7 +1425,7 @@
         <v>5</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47241871755802</v>
+        <v>16.46917095811485</v>
       </c>
     </row>
     <row r="25">
@@ -1466,7 +1466,7 @@
         <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>16.68125211750191</v>
+        <v>16.68150359318814</v>
       </c>
     </row>
     <row r="26">
@@ -1507,7 +1507,7 @@
         <v>5</v>
       </c>
       <c r="K26" t="n">
-        <v>17.13662195006867</v>
+        <v>17.13699864778113</v>
       </c>
     </row>
     <row r="27">
@@ -1548,7 +1548,7 @@
         <v>5</v>
       </c>
       <c r="K27" t="n">
-        <v>17.65643758803501</v>
+        <v>17.65606000717672</v>
       </c>
     </row>
     <row r="28">
@@ -1589,7 +1589,7 @@
         <v>5</v>
       </c>
       <c r="K28" t="n">
-        <v>17.726221843046</v>
+        <v>17.72686803633449</v>
       </c>
     </row>
     <row r="29">
@@ -1630,7 +1630,7 @@
         <v>5</v>
       </c>
       <c r="K29" t="n">
-        <v>17.81936612530993</v>
+        <v>17.81944109171629</v>
       </c>
     </row>
     <row r="30">
@@ -1671,7 +1671,7 @@
         <v>5</v>
       </c>
       <c r="K30" t="n">
-        <v>17.83069852722052</v>
+        <v>17.82989940170764</v>
       </c>
     </row>
     <row r="31">
@@ -1712,7 +1712,7 @@
         <v>5</v>
       </c>
       <c r="K31" t="n">
-        <v>17.91045501285387</v>
+        <v>17.91105143658421</v>
       </c>
     </row>
     <row r="32">
@@ -1753,7 +1753,7 @@
         <v>5</v>
       </c>
       <c r="K32" t="n">
-        <v>18.11075800455528</v>
+        <v>18.11063187715624</v>
       </c>
     </row>
     <row r="33">
@@ -1794,7 +1794,7 @@
         <v>5</v>
       </c>
       <c r="K33" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="34">
@@ -1835,7 +1835,7 @@
         <v>5</v>
       </c>
       <c r="K34" t="n">
-        <v>18.15983980085726</v>
+        <v>18.15987093947113</v>
       </c>
     </row>
     <row r="35">
@@ -1876,7 +1876,7 @@
         <v>5</v>
       </c>
       <c r="K35" t="n">
-        <v>18.25333437977661</v>
+        <v>18.25347872265014</v>
       </c>
     </row>
     <row r="36">
@@ -1917,7 +1917,7 @@
         <v>5</v>
       </c>
       <c r="K36" t="n">
-        <v>18.31313623191253</v>
+        <v>18.31300880162258</v>
       </c>
     </row>
     <row r="37">
@@ -1958,7 +1958,7 @@
         <v>5</v>
       </c>
       <c r="K37" t="n">
-        <v>18.19251281614148</v>
+        <v>18.18374248726346</v>
       </c>
     </row>
     <row r="38">
@@ -1999,7 +1999,7 @@
         <v>5</v>
       </c>
       <c r="K38" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="39">
@@ -2040,7 +2040,7 @@
         <v>5</v>
       </c>
       <c r="K39" t="n">
-        <v>18.32725138968634</v>
+        <v>18.32489867741947</v>
       </c>
     </row>
     <row r="40">
@@ -2081,7 +2081,7 @@
         <v>5</v>
       </c>
       <c r="K40" t="n">
-        <v>18.43101520147438</v>
+        <v>18.43115021407112</v>
       </c>
     </row>
     <row r="41">
@@ -2122,7 +2122,7 @@
         <v>5</v>
       </c>
       <c r="K41" t="n">
-        <v>18.5685952563802</v>
+        <v>18.56838849707095</v>
       </c>
     </row>
     <row r="42">
@@ -2163,7 +2163,7 @@
         <v>5</v>
       </c>
       <c r="K42" t="n">
-        <v>18.58008141167307</v>
+        <v>18.58191783635835</v>
       </c>
     </row>
     <row r="43">
@@ -2204,7 +2204,7 @@
         <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>18.83955821569582</v>
+        <v>18.84045488162381</v>
       </c>
     </row>
     <row r="44">
@@ -2245,7 +2245,7 @@
         <v>5</v>
       </c>
       <c r="K44" t="n">
-        <v>18.7683839298948</v>
+        <v>18.76887581351305</v>
       </c>
     </row>
     <row r="45">
@@ -2286,7 +2286,7 @@
         <v>5</v>
       </c>
       <c r="K45" t="n">
-        <v>18.73776743207468</v>
+        <v>18.74229667334115</v>
       </c>
     </row>
     <row r="46">
@@ -2327,7 +2327,7 @@
         <v>5</v>
       </c>
       <c r="K46" t="n">
-        <v>18.54743048859889</v>
+        <v>18.54653760366034</v>
       </c>
     </row>
     <row r="47">
@@ -2368,7 +2368,7 @@
         <v>5</v>
       </c>
       <c r="K47" t="n">
-        <v>18.15252804766378</v>
+        <v>18.15454817016082</v>
       </c>
     </row>
     <row r="48">
@@ -2409,7 +2409,7 @@
         <v>5</v>
       </c>
       <c r="K48" t="n">
-        <v>18.08003792003841</v>
+        <v>18.08007013293001</v>
       </c>
     </row>
     <row r="49">
@@ -2450,7 +2450,7 @@
         <v>5</v>
       </c>
       <c r="K49" t="n">
-        <v>18.0508829171354</v>
+        <v>18.04915627873921</v>
       </c>
     </row>
     <row r="50">
@@ -2491,7 +2491,7 @@
         <v>5</v>
       </c>
       <c r="K50" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="51">
@@ -2532,7 +2532,7 @@
         <v>5</v>
       </c>
       <c r="K51" t="n">
-        <v>17.99032586218531</v>
+        <v>17.98837875632599</v>
       </c>
     </row>
     <row r="52">
@@ -2573,7 +2573,7 @@
         <v>5</v>
       </c>
       <c r="K52" t="n">
-        <v>17.7490806393877</v>
+        <v>17.74861576103778</v>
       </c>
     </row>
     <row r="53">
@@ -2614,7 +2614,7 @@
         <v>5</v>
       </c>
       <c r="K53" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="54">
@@ -2655,7 +2655,7 @@
         <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>17.74969718700408</v>
+        <v>17.74812266773921</v>
       </c>
     </row>
     <row r="55">
@@ -2696,7 +2696,7 @@
         <v>5</v>
       </c>
       <c r="K55" t="n">
-        <v>17.81814662802715</v>
+        <v>17.79881074691802</v>
       </c>
     </row>
     <row r="56">
@@ -2737,7 +2737,7 @@
         <v>5</v>
       </c>
       <c r="K56" t="n">
-        <v>17.99225470919088</v>
+        <v>17.97859383075771</v>
       </c>
     </row>
     <row r="57">
@@ -2778,7 +2778,7 @@
         <v>5</v>
       </c>
       <c r="K57" t="n">
-        <v>18.04864477364506</v>
+        <v>18.04209307204975</v>
       </c>
     </row>
     <row r="58">
@@ -2819,7 +2819,7 @@
         <v>5</v>
       </c>
       <c r="K58" t="n">
-        <v>18.06393349092241</v>
+        <v>18.05583693465113</v>
       </c>
     </row>
     <row r="59">
@@ -2860,7 +2860,7 @@
         <v>5</v>
       </c>
       <c r="K59" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="60">
@@ -2901,7 +2901,7 @@
         <v>5</v>
       </c>
       <c r="K60" t="n">
-        <v>18.25587384616591</v>
+        <v>18.25537619819129</v>
       </c>
     </row>
     <row r="61">
@@ -2942,7 +2942,7 @@
         <v>5</v>
       </c>
       <c r="K61" t="n">
-        <v>18.26553935250956</v>
+        <v>18.26535630570529</v>
       </c>
     </row>
     <row r="62">
@@ -2983,7 +2983,7 @@
         <v>5</v>
       </c>
       <c r="K62" t="n">
-        <v>18.25615665036968</v>
+        <v>18.25543714052691</v>
       </c>
     </row>
     <row r="63">
@@ -3024,7 +3024,7 @@
         <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>18.32865305918012</v>
+        <v>18.35082486847733</v>
       </c>
     </row>
     <row r="64">
@@ -3065,7 +3065,7 @@
         <v>5</v>
       </c>
       <c r="K64" t="n">
-        <v>18.22115293721825</v>
+        <v>18.31842442556919</v>
       </c>
     </row>
     <row r="65">
@@ -3106,7 +3106,7 @@
         <v>5</v>
       </c>
       <c r="K65" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="66">
@@ -3147,7 +3147,7 @@
         <v>5</v>
       </c>
       <c r="K66" t="n">
-        <v>18.33354581660341</v>
+        <v>18.3533122614999</v>
       </c>
     </row>
     <row r="67">
@@ -3188,7 +3188,7 @@
         <v>5</v>
       </c>
       <c r="K67" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="68">
@@ -3229,7 +3229,7 @@
         <v>5</v>
       </c>
       <c r="K68" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="69">
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="K69" t="n">
-        <v>19.39058911605064</v>
+        <v>18.98502910614225</v>
       </c>
     </row>
     <row r="70">
@@ -3311,7 +3311,7 @@
         <v>5</v>
       </c>
       <c r="K70" t="n">
-        <v>21.66404939438216</v>
+        <v>20.94651363125861</v>
       </c>
     </row>
     <row r="71">
@@ -3352,7 +3352,7 @@
         <v>5</v>
       </c>
       <c r="K71" t="n">
-        <v>21.66404939438216</v>
+        <v>20.94651363125861</v>
       </c>
     </row>
     <row r="72">
@@ -3393,7 +3393,7 @@
         <v>6</v>
       </c>
       <c r="K72" t="n">
-        <v>22.14156626639458</v>
+        <v>21.90771317294598</v>
       </c>
     </row>
     <row r="73">
@@ -3434,7 +3434,7 @@
         <v>6</v>
       </c>
       <c r="K73" t="n">
-        <v>22.16242471488815</v>
+        <v>21.95699867896413</v>
       </c>
     </row>
     <row r="74">
@@ -3475,7 +3475,7 @@
         <v>6</v>
       </c>
       <c r="K74" t="n">
-        <v>23.89073664208809</v>
+        <v>23.78508316000404</v>
       </c>
     </row>
     <row r="75">
@@ -3516,7 +3516,7 @@
         <v>6</v>
       </c>
       <c r="K75" t="n">
-        <v>0.6742643271988668</v>
+        <v>0.6687806371559569</v>
       </c>
     </row>
     <row r="76">
@@ -3557,7 +3557,7 @@
         <v>6</v>
       </c>
       <c r="K76" t="n">
-        <v>0.7252819316670009</v>
+        <v>0.7213389540098346</v>
       </c>
     </row>
     <row r="77">
@@ -3598,7 +3598,7 @@
         <v>6</v>
       </c>
       <c r="K77" t="n">
-        <v>0.7819875890269926</v>
+        <v>0.7791062941235075</v>
       </c>
     </row>
     <row r="78">
@@ -3639,7 +3639,7 @@
         <v>6</v>
       </c>
       <c r="K78" t="n">
-        <v>0.8103286190362372</v>
+        <v>0.8050203406469022</v>
       </c>
     </row>
     <row r="79">
@@ -3680,7 +3680,7 @@
         <v>6</v>
       </c>
       <c r="K79" t="n">
-        <v>25.14243936608069</v>
+        <v>25.09856616014096</v>
       </c>
     </row>
     <row r="80">
@@ -3721,7 +3721,7 @@
         <v>6</v>
       </c>
       <c r="K80" t="n">
-        <v>26.08450755720653</v>
+        <v>26.2404020349576</v>
       </c>
     </row>
     <row r="81">
@@ -3762,7 +3762,7 @@
         <v>6</v>
       </c>
       <c r="K81" t="n">
-        <v>26.27248005679646</v>
+        <v>26.2404020349576</v>
       </c>
     </row>
     <row r="82">
@@ -3803,7 +3803,7 @@
         <v>6</v>
       </c>
       <c r="K82" t="n">
-        <v>28.07173518406669</v>
+        <v>28.15250810073567</v>
       </c>
     </row>
     <row r="83">
@@ -3844,7 +3844,7 @@
         <v>11</v>
       </c>
       <c r="K83" t="n">
-        <v>30.02397104987351</v>
+        <v>30.0723175916815</v>
       </c>
     </row>
     <row r="84">
@@ -3885,7 +3885,7 @@
         <v>11</v>
       </c>
       <c r="K84" t="n">
-        <v>33.93106343073827</v>
+        <v>33.12970607485668</v>
       </c>
     </row>
     <row r="85">
@@ -3926,7 +3926,7 @@
         <v>11</v>
       </c>
       <c r="K85" t="n">
-        <v>33.93106343073827</v>
+        <v>33.12970607485668</v>
       </c>
     </row>
     <row r="86">
@@ -3967,7 +3967,7 @@
         <v>11</v>
       </c>
       <c r="K86" t="n">
-        <v>35.72995783874642</v>
+        <v>35.33464815617634</v>
       </c>
     </row>
     <row r="87">
@@ -4008,7 +4008,7 @@
         <v>11</v>
       </c>
       <c r="K87" t="n">
-        <v>35.55938049603233</v>
+        <v>35.33464815617634</v>
       </c>
     </row>
     <row r="88">
@@ -4049,7 +4049,7 @@
         <v>11</v>
       </c>
       <c r="K88" t="n">
-        <v>34.26020823081542</v>
+        <v>34.32751082832033</v>
       </c>
     </row>
     <row r="89">
@@ -4090,7 +4090,7 @@
         <v>11</v>
       </c>
       <c r="K89" t="n">
-        <v>34.26020823081542</v>
+        <v>33.72263094040903</v>
       </c>
     </row>
     <row r="90">
@@ -4131,7 +4131,7 @@
         <v>11</v>
       </c>
       <c r="K90" t="n">
-        <v>33.60421491792203</v>
+        <v>33.58353956337891</v>
       </c>
     </row>
     <row r="91">
@@ -4172,7 +4172,7 @@
         <v>11</v>
       </c>
       <c r="K91" t="n">
-        <v>32.25732494002654</v>
+        <v>32.46181745415356</v>
       </c>
     </row>
     <row r="92">
@@ -4213,7 +4213,7 @@
         <v>11</v>
       </c>
       <c r="K92" t="n">
-        <v>32.25732494002654</v>
+        <v>31.53057840703528</v>
       </c>
     </row>
     <row r="93">
@@ -4254,7 +4254,7 @@
         <v>11</v>
       </c>
       <c r="K93" t="n">
-        <v>29.5809159019295</v>
+        <v>29.64732090098634</v>
       </c>
     </row>
     <row r="94">
@@ -4295,7 +4295,7 @@
         <v>11</v>
       </c>
       <c r="K94" t="n">
-        <v>28.85260555578949</v>
+        <v>28.84728032399684</v>
       </c>
     </row>
     <row r="95">
@@ -4336,7 +4336,7 @@
         <v>11</v>
       </c>
       <c r="K95" t="n">
-        <v>27.59102216091332</v>
+        <v>27.68572614297149</v>
       </c>
     </row>
     <row r="96">
@@ -4377,7 +4377,7 @@
         <v>11</v>
       </c>
       <c r="K96" t="n">
-        <v>13.58206214581482</v>
+        <v>13.45582952174553</v>
       </c>
     </row>
     <row r="97">
@@ -4418,7 +4418,7 @@
         <v>11</v>
       </c>
       <c r="K97" t="n">
-        <v>14.92850198125039</v>
+        <v>14.92454405059119</v>
       </c>
     </row>
     <row r="98">
@@ -4459,7 +4459,7 @@
         <v>11</v>
       </c>
       <c r="K98" t="n">
-        <v>17.63710851302559</v>
+        <v>17.55510645238489</v>
       </c>
     </row>
     <row r="99">
@@ -4500,7 +4500,7 @@
         <v>11</v>
       </c>
       <c r="K99" t="n">
-        <v>32.50207028708833</v>
+        <v>32.67655883920442</v>
       </c>
     </row>
     <row r="100">
@@ -4541,7 +4541,7 @@
         <v>11</v>
       </c>
       <c r="K100" t="n">
-        <v>32.8854867991345</v>
+        <v>32.67655883920442</v>
       </c>
     </row>
     <row r="101">
@@ -4582,7 +4582,7 @@
         <v>11</v>
       </c>
       <c r="K101" t="n">
-        <v>34.04385643174101</v>
+        <v>34.18326497614485</v>
       </c>
     </row>
     <row r="102">
@@ -4623,7 +4623,7 @@
         <v>11</v>
       </c>
       <c r="K102" t="n">
-        <v>34.8005884430348</v>
+        <v>26.30341888026399</v>
       </c>
     </row>
     <row r="103">
@@ -4664,7 +4664,7 @@
         <v>11</v>
       </c>
       <c r="K103" t="n">
-        <v>34.8005884430348</v>
+        <v>26.30341888026399</v>
       </c>
     </row>
     <row r="104">
@@ -4705,7 +4705,7 @@
         <v>11</v>
       </c>
       <c r="K104" t="n">
-        <v>26.65020320706951</v>
+        <v>29.28176759456571</v>
       </c>
     </row>
     <row r="105">
@@ -4746,7 +4746,7 @@
         <v>11</v>
       </c>
       <c r="K105" t="n">
-        <v>26.65020320706951</v>
+        <v>29.28176759456571</v>
       </c>
     </row>
     <row r="106">
@@ -4787,7 +4787,7 @@
         <v>11</v>
       </c>
       <c r="K106" t="n">
-        <v>30.47228368650138</v>
+        <v>29.69263070332197</v>
       </c>
     </row>
     <row r="107">
@@ -4828,7 +4828,7 @@
         <v>11</v>
       </c>
       <c r="K107" t="n">
-        <v>30.47228368650138</v>
+        <v>29.69263070332197</v>
       </c>
     </row>
     <row r="108">
@@ -4869,7 +4869,7 @@
         <v>11</v>
       </c>
       <c r="K108" t="n">
-        <v>31.57247686638782</v>
+        <v>30.9277383207447</v>
       </c>
     </row>
     <row r="109">
@@ -4910,7 +4910,7 @@
         <v>11</v>
       </c>
       <c r="K109" t="n">
-        <v>30.7051003580383</v>
+        <v>30.48736325109561</v>
       </c>
     </row>
     <row r="110">
@@ -4951,7 +4951,7 @@
         <v>11</v>
       </c>
       <c r="K110" t="n">
-        <v>29.97582284390176</v>
+        <v>29.8339701431021</v>
       </c>
     </row>
     <row r="111">
@@ -4992,7 +4992,7 @@
         <v>11</v>
       </c>
       <c r="K111" t="n">
-        <v>29.97582284390176</v>
+        <v>29.8339701431021</v>
       </c>
     </row>
     <row r="112">
@@ -5033,7 +5033,7 @@
         <v>17</v>
       </c>
       <c r="K112" t="n">
-        <v>27.54307712829354</v>
+        <v>29.97422687701681</v>
       </c>
     </row>
     <row r="113">
@@ -5074,7 +5074,7 @@
         <v>17</v>
       </c>
       <c r="K113" t="n">
-        <v>6.368860332302354</v>
+        <v>6.394229628251723</v>
       </c>
     </row>
     <row r="114">
@@ -5115,7 +5115,7 @@
         <v>17</v>
       </c>
       <c r="K114" t="n">
-        <v>6.243578717985123</v>
+        <v>6.260133337315924</v>
       </c>
     </row>
     <row r="115">
@@ -5156,7 +5156,7 @@
         <v>17</v>
       </c>
       <c r="K115" t="n">
-        <v>6.32730569450491</v>
+        <v>6.304330365346789</v>
       </c>
     </row>
     <row r="116">
@@ -5197,7 +5197,7 @@
         <v>17</v>
       </c>
       <c r="K116" t="n">
-        <v>6.32730569450491</v>
+        <v>6.304330365346789</v>
       </c>
     </row>
     <row r="117">
@@ -5238,7 +5238,7 @@
         <v>17</v>
       </c>
       <c r="K117" t="n">
-        <v>6.392435803687235</v>
+        <v>6.387273696259207</v>
       </c>
     </row>
     <row r="118">
@@ -5279,7 +5279,7 @@
         <v>17</v>
       </c>
       <c r="K118" t="n">
-        <v>6.47837896333867</v>
+        <v>6.45604406382135</v>
       </c>
     </row>
     <row r="119">
@@ -5320,7 +5320,7 @@
         <v>17</v>
       </c>
       <c r="K119" t="n">
-        <v>6.811497567267673</v>
+        <v>6.818788451684092</v>
       </c>
     </row>
     <row r="120">
@@ -5361,7 +5361,7 @@
         <v>17</v>
       </c>
       <c r="K120" t="n">
-        <v>6.811497567267673</v>
+        <v>6.818788451684092</v>
       </c>
     </row>
     <row r="121">
@@ -5402,7 +5402,7 @@
         <v>17</v>
       </c>
       <c r="K121" t="n">
-        <v>6.90473503174959</v>
+        <v>6.892426842023912</v>
       </c>
     </row>
     <row r="122">
@@ -5443,7 +5443,7 @@
         <v>17</v>
       </c>
       <c r="K122" t="n">
-        <v>7.009257984692042</v>
+        <v>7.002731373643452</v>
       </c>
     </row>
     <row r="123">
@@ -5484,7 +5484,7 @@
         <v>17</v>
       </c>
       <c r="K123" t="n">
-        <v>7.009257984692042</v>
+        <v>7.002731373643452</v>
       </c>
     </row>
     <row r="124">
@@ -5525,7 +5525,7 @@
         <v>17</v>
       </c>
       <c r="K124" t="n">
-        <v>7.036662400576596</v>
+        <v>7.03448653682228</v>
       </c>
     </row>
     <row r="125">
@@ -5566,7 +5566,7 @@
         <v>17</v>
       </c>
       <c r="K125" t="n">
-        <v>6.995782921034595</v>
+        <v>6.965222870726626</v>
       </c>
     </row>
     <row r="126">
@@ -5607,7 +5607,7 @@
         <v>17</v>
       </c>
       <c r="K126" t="n">
-        <v>6.939650308981772</v>
+        <v>6.948909992854061</v>
       </c>
     </row>
     <row r="127">
@@ -5648,7 +5648,7 @@
         <v>17</v>
       </c>
       <c r="K127" t="n">
-        <v>6.829262396259586</v>
+        <v>6.844761965900958</v>
       </c>
     </row>
     <row r="128">
@@ -5689,7 +5689,7 @@
         <v>17</v>
       </c>
       <c r="K128" t="n">
-        <v>6.829262396259586</v>
+        <v>6.844761965900958</v>
       </c>
     </row>
     <row r="129">
@@ -5730,7 +5730,7 @@
         <v>17</v>
       </c>
       <c r="K129" t="n">
-        <v>6.739686757437209</v>
+        <v>6.759342622864795</v>
       </c>
     </row>
     <row r="130">
@@ -5771,7 +5771,7 @@
         <v>17</v>
       </c>
       <c r="K130" t="n">
-        <v>6.582992726856799</v>
+        <v>6.602081830291315</v>
       </c>
     </row>
     <row r="131">
@@ -5812,7 +5812,7 @@
         <v>17</v>
       </c>
       <c r="K131" t="n">
-        <v>6.427274373633168</v>
+        <v>6.447913261464199</v>
       </c>
     </row>
     <row r="132">
@@ -5853,7 +5853,7 @@
         <v>17</v>
       </c>
       <c r="K132" t="n">
-        <v>6.427274373633168</v>
+        <v>6.447913261464199</v>
       </c>
     </row>
     <row r="133">
@@ -5894,7 +5894,7 @@
         <v>17</v>
       </c>
       <c r="K133" t="n">
-        <v>6.269097881919837</v>
+        <v>6.286437957577838</v>
       </c>
     </row>
     <row r="134">
@@ -5935,7 +5935,7 @@
         <v>17</v>
       </c>
       <c r="K134" t="n">
-        <v>6.164167181636034</v>
+        <v>6.15366395093655</v>
       </c>
     </row>
     <row r="135">
@@ -5976,7 +5976,7 @@
         <v>17</v>
       </c>
       <c r="K135" t="n">
-        <v>6.140849187586153</v>
+        <v>6.15366395093655</v>
       </c>
     </row>
     <row r="136">
@@ -6017,7 +6017,7 @@
         <v>17</v>
       </c>
       <c r="K136" t="n">
-        <v>5.882482856253138</v>
+        <v>5.893461410381708</v>
       </c>
     </row>
     <row r="137">
@@ -6058,7 +6058,7 @@
         <v>17</v>
       </c>
       <c r="K137" t="n">
-        <v>5.736315390548596</v>
+        <v>5.718947930533291</v>
       </c>
     </row>
     <row r="138">
@@ -6099,7 +6099,7 @@
         <v>17</v>
       </c>
       <c r="K138" t="n">
-        <v>5.710260936669161</v>
+        <v>5.712852643823005</v>
       </c>
     </row>
     <row r="139">
@@ -6140,7 +6140,7 @@
         <v>17</v>
       </c>
       <c r="K139" t="n">
-        <v>5.700222144927777</v>
+        <v>5.692598254015039</v>
       </c>
     </row>
     <row r="140">
@@ -6181,7 +6181,7 @@
         <v>17</v>
       </c>
       <c r="K140" t="n">
-        <v>5.711040344275069</v>
+        <v>5.704902857121272</v>
       </c>
     </row>
     <row r="141">
@@ -6222,7 +6222,7 @@
         <v>17</v>
       </c>
       <c r="K141" t="n">
-        <v>6.291535480176309</v>
+        <v>6.26230317497177</v>
       </c>
     </row>
     <row r="142">
@@ -6263,7 +6263,7 @@
         <v>17</v>
       </c>
       <c r="K142" t="n">
-        <v>6.552454352023732</v>
+        <v>6.524154597168152</v>
       </c>
     </row>
     <row r="143">
@@ -6304,7 +6304,7 @@
         <v>17</v>
       </c>
       <c r="K143" t="n">
-        <v>6.763428747104236</v>
+        <v>6.738221031280524</v>
       </c>
     </row>
     <row r="144">
@@ -6345,7 +6345,7 @@
         <v>17</v>
       </c>
       <c r="K144" t="n">
-        <v>6.97259129945409</v>
+        <v>7.105702445742474</v>
       </c>
     </row>
     <row r="145">
@@ -6386,7 +6386,7 @@
         <v>17</v>
       </c>
       <c r="K145" t="n">
-        <v>7.314747643483888</v>
+        <v>7.302580157059705</v>
       </c>
     </row>
     <row r="146">
@@ -6427,7 +6427,7 @@
         <v>17</v>
       </c>
       <c r="K146" t="n">
-        <v>7.402053625346182</v>
+        <v>7.393033836462709</v>
       </c>
     </row>
     <row r="147">
@@ -6468,7 +6468,7 @@
         <v>17</v>
       </c>
       <c r="K147" t="n">
-        <v>7.452460401670667</v>
+        <v>7.45406944170762</v>
       </c>
     </row>
     <row r="148">
@@ -6509,7 +6509,7 @@
         <v>17</v>
       </c>
       <c r="K148" t="n">
-        <v>7.137690582644701</v>
+        <v>7.151236587484997</v>
       </c>
     </row>
     <row r="149">
@@ -6550,7 +6550,7 @@
         <v>17</v>
       </c>
       <c r="K149" t="n">
-        <v>7.060329402812143</v>
+        <v>7.073587254435585</v>
       </c>
     </row>
     <row r="150">
@@ -6591,7 +6591,7 @@
         <v>17</v>
       </c>
       <c r="K150" t="n">
-        <v>7.060329402812143</v>
+        <v>7.073587254435585</v>
       </c>
     </row>
     <row r="151">
@@ -6632,7 +6632,7 @@
         <v>17</v>
       </c>
       <c r="K151" t="n">
-        <v>7.040948934445939</v>
+        <v>6.989288158253655</v>
       </c>
     </row>
     <row r="152">
@@ -6673,7 +6673,7 @@
         <v>17</v>
       </c>
       <c r="K152" t="n">
-        <v>6.715020032112586</v>
+        <v>6.63956582671167</v>
       </c>
     </row>
     <row r="153">
@@ -6714,7 +6714,7 @@
         <v>17</v>
       </c>
       <c r="K153" t="n">
-        <v>6.338791090776827</v>
+        <v>6.363712727227157</v>
       </c>
     </row>
     <row r="154">
@@ -6755,7 +6755,7 @@
         <v>17</v>
       </c>
       <c r="K154" t="n">
-        <v>6.178996684265116</v>
+        <v>6.206880308422047</v>
       </c>
     </row>
     <row r="155">
@@ -6796,7 +6796,7 @@
         <v>17</v>
       </c>
       <c r="K155" t="n">
-        <v>6.000334894592796</v>
+        <v>6.031544329445902</v>
       </c>
     </row>
     <row r="156">
@@ -6837,7 +6837,7 @@
         <v>17</v>
       </c>
       <c r="K156" t="n">
-        <v>5.329949029981647</v>
+        <v>5.350677701696725</v>
       </c>
     </row>
     <row r="157">
@@ -6878,7 +6878,7 @@
         <v>17</v>
       </c>
       <c r="K157" t="n">
-        <v>5.192684241831878</v>
+        <v>5.203348639064105</v>
       </c>
     </row>
     <row r="158">
@@ -6919,7 +6919,7 @@
         <v>17</v>
       </c>
       <c r="K158" t="n">
-        <v>5.034796515651481</v>
+        <v>5.042390611054621</v>
       </c>
     </row>
     <row r="159">
@@ -6960,7 +6960,7 @@
         <v>17</v>
       </c>
       <c r="K159" t="n">
-        <v>5.156053736591606</v>
+        <v>5.136348955563021</v>
       </c>
     </row>
     <row r="160">
@@ -7001,7 +7001,7 @@
         <v>17</v>
       </c>
       <c r="K160" t="n">
-        <v>5.57742993932842</v>
+        <v>5.55144672363453</v>
       </c>
     </row>
     <row r="161">
@@ -7042,7 +7042,7 @@
         <v>17</v>
       </c>
       <c r="K161" t="n">
-        <v>5.747734269282226</v>
+        <v>5.776322621998234</v>
       </c>
     </row>
     <row r="162">
@@ -7083,7 +7083,7 @@
         <v>17</v>
       </c>
       <c r="K162" t="n">
-        <v>6.261073493671605</v>
+        <v>6.248919972144285</v>
       </c>
     </row>
     <row r="163">
@@ -7124,7 +7124,7 @@
         <v>17</v>
       </c>
       <c r="K163" t="n">
-        <v>6.3509692844717</v>
+        <v>6.344427982629672</v>
       </c>
     </row>
     <row r="164">
@@ -7165,7 +7165,7 @@
         <v>17</v>
       </c>
       <c r="K164" t="n">
-        <v>6.426002307031754</v>
+        <v>6.43150528916774</v>
       </c>
     </row>
     <row r="165">
@@ -7206,7 +7206,7 @@
         <v>17</v>
       </c>
       <c r="K165" t="n">
-        <v>6.493814413278744</v>
+        <v>6.498408830801671</v>
       </c>
     </row>
     <row r="166">
@@ -7247,7 +7247,7 @@
         <v>17</v>
       </c>
       <c r="K166" t="n">
-        <v>6.493814413278744</v>
+        <v>6.498408830801671</v>
       </c>
     </row>
     <row r="167">
@@ -7288,7 +7288,7 @@
         <v>17</v>
       </c>
       <c r="K167" t="n">
-        <v>6.484449522851524</v>
+        <v>6.490944130896361</v>
       </c>
     </row>
     <row r="168">
@@ -7329,7 +7329,7 @@
         <v>17</v>
       </c>
       <c r="K168" t="n">
-        <v>6.296829148845255</v>
+        <v>6.30590760246487</v>
       </c>
     </row>
     <row r="169">
@@ -7370,7 +7370,7 @@
         <v>17</v>
       </c>
       <c r="K169" t="n">
-        <v>6.296829148845255</v>
+        <v>6.30590760246487</v>
       </c>
     </row>
     <row r="170">
@@ -7411,7 +7411,7 @@
         <v>17</v>
       </c>
       <c r="K170" t="n">
-        <v>6.252126694619706</v>
+        <v>6.243775251025913</v>
       </c>
     </row>
     <row r="171">
@@ -7452,7 +7452,7 @@
         <v>17</v>
       </c>
       <c r="K171" t="n">
-        <v>6.158763854286831</v>
+        <v>6.168429468307566</v>
       </c>
     </row>
     <row r="172">
@@ -7493,7 +7493,7 @@
         <v>17</v>
       </c>
       <c r="K172" t="n">
-        <v>6.096264577712642</v>
+        <v>6.084313006567648</v>
       </c>
     </row>
     <row r="173">
@@ -7534,7 +7534,7 @@
         <v>17</v>
       </c>
       <c r="K173" t="n">
-        <v>6.018298821252825</v>
+        <v>6.032455212563289</v>
       </c>
     </row>
     <row r="174">
@@ -7575,7 +7575,7 @@
         <v>17</v>
       </c>
       <c r="K174" t="n">
-        <v>5.80423300936083</v>
+        <v>5.824560652973466</v>
       </c>
     </row>
     <row r="175">
@@ -7616,7 +7616,7 @@
         <v>17</v>
       </c>
       <c r="K175" t="n">
-        <v>5.80423300936083</v>
+        <v>5.783411711045866</v>
       </c>
     </row>
     <row r="176">
@@ -7657,7 +7657,7 @@
         <v>17</v>
       </c>
       <c r="K176" t="n">
-        <v>5.770125749880156</v>
+        <v>5.783411711045866</v>
       </c>
     </row>
     <row r="177">
@@ -7698,7 +7698,7 @@
         <v>17</v>
       </c>
       <c r="K177" t="n">
-        <v>5.246029265980684</v>
+        <v>5.273689208370009</v>
       </c>
     </row>
     <row r="178">
@@ -7739,7 +7739,7 @@
         <v>17</v>
       </c>
       <c r="K178" t="n">
-        <v>5.246029265980684</v>
+        <v>5.217788954896063</v>
       </c>
     </row>
     <row r="179">
@@ -7780,7 +7780,7 @@
         <v>17</v>
       </c>
       <c r="K179" t="n">
-        <v>4.912754819939559</v>
+        <v>4.883659247979038</v>
       </c>
     </row>
     <row r="180">
@@ -7821,7 +7821,7 @@
         <v>17</v>
       </c>
       <c r="K180" t="n">
-        <v>4.866380783143212</v>
+        <v>4.784665552852319</v>
       </c>
     </row>
     <row r="181">
@@ -7862,7 +7862,7 @@
         <v>17</v>
       </c>
       <c r="K181" t="n">
-        <v>4.626524534169275</v>
+        <v>4.631261157514952</v>
       </c>
     </row>
     <row r="182">
@@ -7903,7 +7903,7 @@
         <v>17</v>
       </c>
       <c r="K182" t="n">
-        <v>4.626524534169275</v>
+        <v>4.631261157514952</v>
       </c>
     </row>
     <row r="183">
@@ -7944,7 +7944,7 @@
         <v>17</v>
       </c>
       <c r="K183" t="n">
-        <v>4.680974129789471</v>
+        <v>4.672467824556563</v>
       </c>
     </row>
     <row r="184">
@@ -7985,7 +7985,7 @@
         <v>17</v>
       </c>
       <c r="K184" t="n">
-        <v>4.697421348352245</v>
+        <v>4.691065899382967</v>
       </c>
     </row>
     <row r="185">
@@ -8026,7 +8026,7 @@
         <v>17</v>
       </c>
       <c r="K185" t="n">
-        <v>4.970390325833943</v>
+        <v>4.959985830152203</v>
       </c>
     </row>
     <row r="186">
@@ -8067,7 +8067,7 @@
         <v>17</v>
       </c>
       <c r="K186" t="n">
-        <v>5.042033068436351</v>
+        <v>5.061964276895472</v>
       </c>
     </row>
     <row r="187">
@@ -8108,7 +8108,7 @@
         <v>17</v>
       </c>
       <c r="K187" t="n">
-        <v>5.144273510192376</v>
+        <v>5.139621947657399</v>
       </c>
     </row>
     <row r="188">
@@ -8149,7 +8149,7 @@
         <v>17</v>
       </c>
       <c r="K188" t="n">
-        <v>5.151181089022467</v>
+        <v>5.155013385865095</v>
       </c>
     </row>
     <row r="189">
@@ -8190,7 +8190,7 @@
         <v>17</v>
       </c>
       <c r="K189" t="n">
-        <v>5.127630386390929</v>
+        <v>5.131134106491538</v>
       </c>
     </row>
     <row r="190">
@@ -8231,7 +8231,7 @@
         <v>17</v>
       </c>
       <c r="K190" t="n">
-        <v>5.123446376741982</v>
+        <v>5.124655550525722</v>
       </c>
     </row>
     <row r="191">
@@ -8272,7 +8272,7 @@
         <v>17</v>
       </c>
       <c r="K191" t="n">
-        <v>5.126603929821988</v>
+        <v>5.134248956556644</v>
       </c>
     </row>
     <row r="192">
@@ -8313,7 +8313,7 @@
         <v>17</v>
       </c>
       <c r="K192" t="n">
-        <v>5.139644963111619</v>
+        <v>5.139100160208838</v>
       </c>
     </row>
     <row r="193">
@@ -8354,7 +8354,7 @@
         <v>17</v>
       </c>
       <c r="K193" t="n">
-        <v>5.139131518439145</v>
+        <v>5.13581627233214</v>
       </c>
     </row>
     <row r="194">
@@ -8395,7 +8395,7 @@
         <v>17</v>
       </c>
       <c r="K194" t="n">
-        <v>5.133982178218036</v>
+        <v>5.13581627233214</v>
       </c>
     </row>
     <row r="195">
@@ -8436,7 +8436,7 @@
         <v>17</v>
       </c>
       <c r="K195" t="n">
-        <v>5.121538876501863</v>
+        <v>5.117998934186575</v>
       </c>
     </row>
     <row r="196">
@@ -8477,7 +8477,7 @@
         <v>17</v>
       </c>
       <c r="K196" t="n">
-        <v>5.087714003405997</v>
+        <v>5.090020584402274</v>
       </c>
     </row>
     <row r="197">
@@ -8518,7 +8518,7 @@
         <v>17</v>
       </c>
       <c r="K197" t="n">
-        <v>5.068168270738139</v>
+        <v>5.065475118317499</v>
       </c>
     </row>
     <row r="198">
@@ -8559,7 +8559,7 @@
         <v>17</v>
       </c>
       <c r="K198" t="n">
-        <v>5.08878105473769</v>
+        <v>5.095656792811958</v>
       </c>
     </row>
     <row r="199">
@@ -8600,7 +8600,7 @@
         <v>17</v>
       </c>
       <c r="K199" t="n">
-        <v>5.115815920964135</v>
+        <v>5.111366260963839</v>
       </c>
     </row>
     <row r="200">
@@ -8641,7 +8641,7 @@
         <v>17</v>
       </c>
       <c r="K200" t="n">
-        <v>5.184305404881255</v>
+        <v>5.181655880515361</v>
       </c>
     </row>
     <row r="201">
@@ -8682,7 +8682,7 @@
         <v>17</v>
       </c>
       <c r="K201" t="n">
-        <v>5.282291494160479</v>
+        <v>5.275935643321246</v>
       </c>
     </row>
     <row r="202">
@@ -8723,7 +8723,7 @@
         <v>17</v>
       </c>
       <c r="K202" t="n">
-        <v>5.306780504641036</v>
+        <v>5.305149569350647</v>
       </c>
     </row>
     <row r="203">
@@ -8764,7 +8764,7 @@
         <v>17</v>
       </c>
       <c r="K203" t="n">
-        <v>5.313776092214001</v>
+        <v>5.302422547583889</v>
       </c>
     </row>
     <row r="204">
@@ -8805,7 +8805,7 @@
         <v>17</v>
       </c>
       <c r="K204" t="n">
-        <v>5.237580264031222</v>
+        <v>5.228526939231704</v>
       </c>
     </row>
     <row r="205">
@@ -8846,7 +8846,7 @@
         <v>17</v>
       </c>
       <c r="K205" t="n">
-        <v>5.224129951944697</v>
+        <v>5.200979142360072</v>
       </c>
     </row>
     <row r="206">
@@ -8887,7 +8887,7 @@
         <v>17</v>
       </c>
       <c r="K206" t="n">
-        <v>5.120875290181623</v>
+        <v>5.134218922524557</v>
       </c>
     </row>
     <row r="207">
@@ -8928,7 +8928,7 @@
         <v>17</v>
       </c>
       <c r="K207" t="n">
-        <v>5.030314551344453</v>
+        <v>5.006731259254795</v>
       </c>
     </row>
     <row r="208">
@@ -8969,7 +8969,7 @@
         <v>17</v>
       </c>
       <c r="K208" t="n">
-        <v>4.837855262593338</v>
+        <v>4.839940779892678</v>
       </c>
     </row>
     <row r="209">
@@ -9010,7 +9010,7 @@
         <v>17</v>
       </c>
       <c r="K209" t="n">
-        <v>4.869418055800006</v>
+        <v>4.863411672434975</v>
       </c>
     </row>
     <row r="210">
@@ -9051,7 +9051,7 @@
         <v>17</v>
       </c>
       <c r="K210" t="n">
-        <v>4.909595072075414</v>
+        <v>4.90238404482472</v>
       </c>
     </row>
     <row r="211">
@@ -9092,7 +9092,7 @@
         <v>17</v>
       </c>
       <c r="K211" t="n">
-        <v>5.211543687537375</v>
+        <v>5.189791705669578</v>
       </c>
     </row>
     <row r="212">
@@ -9133,7 +9133,7 @@
         <v>17</v>
       </c>
       <c r="K212" t="n">
-        <v>5.471331558169839</v>
+        <v>5.454828256217485</v>
       </c>
     </row>
     <row r="213">
@@ -9174,7 +9174,7 @@
         <v>17</v>
       </c>
       <c r="K213" t="n">
-        <v>5.471331558169839</v>
+        <v>5.454828256217485</v>
       </c>
     </row>
     <row r="214">
@@ -9215,7 +9215,7 @@
         <v>17</v>
       </c>
       <c r="K214" t="n">
-        <v>5.750204904186787</v>
+        <v>5.737340673395843</v>
       </c>
     </row>
     <row r="215">
@@ -9256,7 +9256,7 @@
         <v>17</v>
       </c>
       <c r="K215" t="n">
-        <v>5.829844563591625</v>
+        <v>5.821570440480223</v>
       </c>
     </row>
     <row r="216">
@@ -9297,7 +9297,7 @@
         <v>17</v>
       </c>
       <c r="K216" t="n">
-        <v>6.000145621641684</v>
+        <v>5.992020214536216</v>
       </c>
     </row>
     <row r="217">
@@ -9338,7 +9338,7 @@
         <v>17</v>
       </c>
       <c r="K217" t="n">
-        <v>6.824533304730388</v>
+        <v>7.312718667297688</v>
       </c>
     </row>
     <row r="218">
@@ -9379,7 +9379,7 @@
         <v>17</v>
       </c>
       <c r="K218" t="n">
-        <v>6.824533304730388</v>
+        <v>7.312718667297688</v>
       </c>
     </row>
     <row r="219">
@@ -9420,7 +9420,7 @@
         <v>17</v>
       </c>
       <c r="K219" t="n">
-        <v>6.824533304730388</v>
+        <v>7.312718667297688</v>
       </c>
     </row>
     <row r="220">
@@ -9461,7 +9461,7 @@
         <v>17</v>
       </c>
       <c r="K220" t="n">
-        <v>8.240315445993637</v>
+        <v>8.019570673134037</v>
       </c>
     </row>
     <row r="221">
@@ -9502,7 +9502,7 @@
         <v>17</v>
       </c>
       <c r="K221" t="n">
-        <v>8.826393367288581</v>
+        <v>8.683324582782372</v>
       </c>
     </row>
     <row r="222">
@@ -9543,7 +9543,7 @@
         <v>17</v>
       </c>
       <c r="K222" t="n">
-        <v>8.826393367288581</v>
+        <v>8.683324582782372</v>
       </c>
     </row>
     <row r="223">
@@ -9584,7 +9584,7 @@
         <v>17</v>
       </c>
       <c r="K223" t="n">
-        <v>9.329609452879314</v>
+        <v>9.228399817067158</v>
       </c>
     </row>
     <row r="224">
@@ -9625,7 +9625,7 @@
         <v>17</v>
       </c>
       <c r="K224" t="n">
-        <v>9.723716896560067</v>
+        <v>9.961672704425601</v>
       </c>
     </row>
     <row r="225">
@@ -9666,7 +9666,7 @@
         <v>17</v>
       </c>
       <c r="K225" t="n">
-        <v>10.03307424832479</v>
+        <v>10.04932379522304</v>
       </c>
     </row>
     <row r="226">
@@ -9707,7 +9707,7 @@
         <v>17</v>
       </c>
       <c r="K226" t="n">
-        <v>4.856632351407046</v>
+        <v>9.769883178349298</v>
       </c>
     </row>
     <row r="227">
@@ -9748,7 +9748,7 @@
         <v>17</v>
       </c>
       <c r="K227" t="n">
-        <v>4.609437902532792</v>
+        <v>4.606366002301267</v>
       </c>
     </row>
     <row r="228">
@@ -9789,7 +9789,7 @@
         <v>17</v>
       </c>
       <c r="K228" t="n">
-        <v>4.609437902532792</v>
+        <v>4.606366002301267</v>
       </c>
     </row>
     <row r="229">
@@ -9830,7 +9830,7 @@
         <v>17</v>
       </c>
       <c r="K229" t="n">
-        <v>4.671239208686202</v>
+        <v>4.664510882658365</v>
       </c>
     </row>
     <row r="230">
@@ -9871,7 +9871,7 @@
         <v>17</v>
       </c>
       <c r="K230" t="n">
-        <v>4.711501326842547</v>
+        <v>4.742312351433133</v>
       </c>
     </row>
     <row r="231">
@@ -9912,7 +9912,7 @@
         <v>17</v>
       </c>
       <c r="K231" t="n">
-        <v>4.782068855822544</v>
+        <v>4.772179350525374</v>
       </c>
     </row>
     <row r="232">
@@ -9953,7 +9953,7 @@
         <v>17</v>
       </c>
       <c r="K232" t="n">
-        <v>4.821961918514729</v>
+        <v>4.818777016577393</v>
       </c>
     </row>
     <row r="233">
@@ -9994,7 +9994,7 @@
         <v>17</v>
       </c>
       <c r="K233" t="n">
-        <v>4.821961918514729</v>
+        <v>4.818777016577393</v>
       </c>
     </row>
     <row r="234">
@@ -10035,7 +10035,7 @@
         <v>17</v>
       </c>
       <c r="K234" t="n">
-        <v>4.821961918514729</v>
+        <v>4.818777016577393</v>
       </c>
     </row>
     <row r="235">
@@ -10076,7 +10076,7 @@
         <v>17</v>
       </c>
       <c r="K235" t="n">
-        <v>4.829608423758081</v>
+        <v>4.827149290729712</v>
       </c>
     </row>
     <row r="236">
@@ -10117,7 +10117,7 @@
         <v>17</v>
       </c>
       <c r="K236" t="n">
-        <v>4.829608423758081</v>
+        <v>4.827149290729712</v>
       </c>
     </row>
     <row r="237">
@@ -10158,7 +10158,7 @@
         <v>17</v>
       </c>
       <c r="K237" t="n">
-        <v>4.829608423758081</v>
+        <v>4.827149290729712</v>
       </c>
     </row>
     <row r="238">
@@ -10199,7 +10199,7 @@
         <v>17</v>
       </c>
       <c r="K238" t="n">
-        <v>4.816056257086136</v>
+        <v>4.818113384913813</v>
       </c>
     </row>
     <row r="239">
@@ -10240,7 +10240,7 @@
         <v>17</v>
       </c>
       <c r="K239" t="n">
-        <v>4.816056257086136</v>
+        <v>4.818113384913813</v>
       </c>
     </row>
     <row r="240">
@@ -10281,7 +10281,7 @@
         <v>17</v>
       </c>
       <c r="K240" t="n">
-        <v>4.762057408818157</v>
+        <v>4.767516608255364</v>
       </c>
     </row>
     <row r="241">
@@ -10322,7 +10322,7 @@
         <v>17</v>
       </c>
       <c r="K241" t="n">
-        <v>4.762057408818157</v>
+        <v>4.767516608255364</v>
       </c>
     </row>
     <row r="242">
@@ -10363,7 +10363,7 @@
         <v>17</v>
       </c>
       <c r="K242" t="n">
-        <v>4.720825636286269</v>
+        <v>4.727124100343387</v>
       </c>
     </row>
     <row r="243">
@@ -10404,7 +10404,7 @@
         <v>17</v>
       </c>
       <c r="K243" t="n">
-        <v>4.683636001986127</v>
+        <v>4.68900405696896</v>
       </c>
     </row>
     <row r="244">
@@ -10445,7 +10445,7 @@
         <v>17</v>
       </c>
       <c r="K244" t="n">
-        <v>4.651806427907428</v>
+        <v>4.655708910055675</v>
       </c>
     </row>
     <row r="245">
@@ -10486,7 +10486,7 @@
         <v>17</v>
       </c>
       <c r="K245" t="n">
-        <v>4.635479361810469</v>
+        <v>4.634360324327593</v>
       </c>
     </row>
     <row r="246">
@@ -10527,7 +10527,7 @@
         <v>17</v>
       </c>
       <c r="K246" t="n">
-        <v>4.624360968244458</v>
+        <v>4.597904565348499</v>
       </c>
     </row>
     <row r="247">
@@ -10568,7 +10568,7 @@
         <v>17</v>
       </c>
       <c r="K247" t="n">
-        <v>4.539597242009505</v>
+        <v>4.54927754328646</v>
       </c>
     </row>
     <row r="248">
@@ -10609,7 +10609,7 @@
         <v>17</v>
       </c>
       <c r="K248" t="n">
-        <v>4.479800628332337</v>
+        <v>4.488921372425573</v>
       </c>
     </row>
     <row r="249">
@@ -10650,7 +10650,7 @@
         <v>17</v>
       </c>
       <c r="K249" t="n">
-        <v>4.479800628332337</v>
+        <v>4.488921372425573</v>
       </c>
     </row>
     <row r="250">
@@ -10691,7 +10691,7 @@
         <v>17</v>
       </c>
       <c r="K250" t="n">
-        <v>4.479800628332337</v>
+        <v>4.420565116336994</v>
       </c>
     </row>
     <row r="251">
@@ -10732,7 +10732,7 @@
         <v>17</v>
       </c>
       <c r="K251" t="n">
-        <v>4.228232823924721</v>
+        <v>4.242401780839924</v>
       </c>
     </row>
     <row r="252">
@@ -10773,7 +10773,7 @@
         <v>17</v>
       </c>
       <c r="K252" t="n">
-        <v>4.134101208853114</v>
+        <v>4.148810628535121</v>
       </c>
     </row>
     <row r="253">
@@ -10814,7 +10814,7 @@
         <v>17</v>
       </c>
       <c r="K253" t="n">
-        <v>4.134101208853114</v>
+        <v>4.043090087318777</v>
       </c>
     </row>
     <row r="254">
@@ -10855,7 +10855,7 @@
         <v>17</v>
       </c>
       <c r="K254" t="n">
-        <v>3.905942361986198</v>
+        <v>3.923628504956598</v>
       </c>
     </row>
     <row r="255">
@@ -10896,7 +10896,7 @@
         <v>17</v>
       </c>
       <c r="K255" t="n">
-        <v>3.795946572521168</v>
+        <v>3.811697881927334</v>
       </c>
     </row>
     <row r="256">
@@ -10937,7 +10937,7 @@
         <v>17</v>
       </c>
       <c r="K256" t="n">
-        <v>3.71018192805208</v>
+        <v>3.720082564600359</v>
       </c>
     </row>
     <row r="257">
@@ -10978,7 +10978,7 @@
         <v>17</v>
       </c>
       <c r="K257" t="n">
-        <v>3.71018192805208</v>
+        <v>3.720082564600359</v>
       </c>
     </row>
     <row r="258">
@@ -11019,7 +11019,7 @@
         <v>17</v>
       </c>
       <c r="K258" t="n">
-        <v>3.665532459325112</v>
+        <v>3.629522274974029</v>
       </c>
     </row>
     <row r="259">
@@ -11060,7 +11060,7 @@
         <v>17</v>
       </c>
       <c r="K259" t="n">
-        <v>3.622779044827931</v>
+        <v>3.629522274974029</v>
       </c>
     </row>
     <row r="260">
@@ -11101,7 +11101,7 @@
         <v>17</v>
       </c>
       <c r="K260" t="n">
-        <v>3.573795866110739</v>
+        <v>3.582294755000562</v>
       </c>
     </row>
     <row r="261">
@@ -11142,7 +11142,7 @@
         <v>17</v>
       </c>
       <c r="K261" t="n">
-        <v>3.51197624276233</v>
+        <v>3.515164138967755</v>
       </c>
     </row>
     <row r="262">
@@ -11183,7 +11183,7 @@
         <v>17</v>
       </c>
       <c r="K262" t="n">
-        <v>3.503046382163287</v>
+        <v>3.502803988040571</v>
       </c>
     </row>
     <row r="263">
@@ -11224,7 +11224,7 @@
         <v>17</v>
       </c>
       <c r="K263" t="n">
-        <v>3.64417939573038</v>
+        <v>3.637656535485296</v>
       </c>
     </row>
     <row r="264">
@@ -11265,7 +11265,7 @@
         <v>17</v>
       </c>
       <c r="K264" t="n">
-        <v>3.748282892700233</v>
+        <v>3.740233919141569</v>
       </c>
     </row>
     <row r="265">
@@ -11306,7 +11306,7 @@
         <v>17</v>
       </c>
       <c r="K265" t="n">
-        <v>3.748282892700233</v>
+        <v>3.740233919141569</v>
       </c>
     </row>
     <row r="266">
@@ -11347,7 +11347,7 @@
         <v>17</v>
       </c>
       <c r="K266" t="n">
-        <v>3.838316265219945</v>
+        <v>3.832447312097865</v>
       </c>
     </row>
     <row r="267">
@@ -11388,7 +11388,7 @@
         <v>17</v>
       </c>
       <c r="K267" t="n">
-        <v>3.915165718103293</v>
+        <v>3.909838143296338</v>
       </c>
     </row>
     <row r="268">
@@ -11429,7 +11429,7 @@
         <v>17</v>
       </c>
       <c r="K268" t="n">
-        <v>3.915165718103293</v>
+        <v>3.940956009781937</v>
       </c>
     </row>
     <row r="269">
@@ -11470,7 +11470,7 @@
         <v>17</v>
       </c>
       <c r="K269" t="n">
-        <v>3.96890047270169</v>
+        <v>3.967555683488354</v>
       </c>
     </row>
     <row r="270">
@@ -11511,7 +11511,7 @@
         <v>17</v>
       </c>
       <c r="K270" t="n">
-        <v>3.976289604215983</v>
+        <v>3.9751202861733</v>
       </c>
     </row>
     <row r="271">
@@ -11552,7 +11552,7 @@
         <v>17</v>
       </c>
       <c r="K271" t="n">
-        <v>3.976289604215983</v>
+        <v>3.977593060587237</v>
       </c>
     </row>
     <row r="272">
@@ -11593,7 +11593,7 @@
         <v>17</v>
       </c>
       <c r="K272" t="n">
-        <v>3.976693653919785</v>
+        <v>3.963593676746309</v>
       </c>
     </row>
     <row r="273">
@@ -11634,7 +11634,7 @@
         <v>17</v>
       </c>
       <c r="K273" t="n">
-        <v>3.959473001331297</v>
+        <v>3.963593676746309</v>
       </c>
     </row>
     <row r="274">
@@ -11675,7 +11675,7 @@
         <v>17</v>
       </c>
       <c r="K274" t="n">
-        <v>3.908675586608994</v>
+        <v>3.910442346373775</v>
       </c>
     </row>
     <row r="275">
@@ -11716,7 +11716,7 @@
         <v>17</v>
       </c>
       <c r="K275" t="n">
-        <v>3.908675586608994</v>
+        <v>3.910442346373775</v>
       </c>
     </row>
     <row r="276">
@@ -11757,7 +11757,7 @@
         <v>17</v>
       </c>
       <c r="K276" t="n">
-        <v>3.873303660391847</v>
+        <v>3.875367343961519</v>
       </c>
     </row>
     <row r="277">
@@ -11798,7 +11798,7 @@
         <v>17</v>
       </c>
       <c r="K277" t="n">
-        <v>3.873303660391847</v>
+        <v>3.875367343961519</v>
       </c>
     </row>
     <row r="278">
@@ -11839,7 +11839,7 @@
         <v>17</v>
       </c>
       <c r="K278" t="n">
-        <v>3.854884955108721</v>
+        <v>3.838318826415147</v>
       </c>
     </row>
     <row r="279">
@@ -11880,7 +11880,7 @@
         <v>17</v>
       </c>
       <c r="K279" t="n">
-        <v>3.795512218898782</v>
+        <v>3.802037008563245</v>
       </c>
     </row>
     <row r="280">
@@ -11921,7 +11921,7 @@
         <v>17</v>
       </c>
       <c r="K280" t="n">
-        <v>3.795512218898782</v>
+        <v>3.802037008563245</v>
       </c>
     </row>
     <row r="281">
@@ -11962,7 +11962,7 @@
         <v>17</v>
       </c>
       <c r="K281" t="n">
-        <v>3.795512218898782</v>
+        <v>3.802037008563245</v>
       </c>
     </row>
     <row r="282">
@@ -12003,7 +12003,7 @@
         <v>17</v>
       </c>
       <c r="K282" t="n">
-        <v>3.560314610185074</v>
+        <v>3.567954314490782</v>
       </c>
     </row>
     <row r="283">
@@ -12044,7 +12044,7 @@
         <v>17</v>
       </c>
       <c r="K283" t="n">
-        <v>3.41343204341614</v>
+        <v>3.382876447445812</v>
       </c>
     </row>
     <row r="284">
@@ -12085,7 +12085,7 @@
         <v>17</v>
       </c>
       <c r="K284" t="n">
-        <v>3.414903582764012</v>
+        <v>3.408583035370641</v>
       </c>
     </row>
     <row r="285">
@@ -12126,7 +12126,7 @@
         <v>17</v>
       </c>
       <c r="K285" t="n">
-        <v>3.5293708540207</v>
+        <v>3.519094744673152</v>
       </c>
     </row>
     <row r="286">
@@ -12167,7 +12167,7 @@
         <v>17</v>
       </c>
       <c r="K286" t="n">
-        <v>3.5293708540207</v>
+        <v>3.519094744673152</v>
       </c>
     </row>
     <row r="287">
@@ -12208,7 +12208,7 @@
         <v>17</v>
       </c>
       <c r="K287" t="n">
-        <v>3.5293708540207</v>
+        <v>3.600954051389113</v>
       </c>
     </row>
     <row r="288">
@@ -12249,7 +12249,7 @@
         <v>17</v>
       </c>
       <c r="K288" t="n">
-        <v>3.694820829356694</v>
+        <v>3.691766121220716</v>
       </c>
     </row>
     <row r="289">
@@ -12290,7 +12290,7 @@
         <v>17</v>
       </c>
       <c r="K289" t="n">
-        <v>3.693011127907449</v>
+        <v>3.671447104625428</v>
       </c>
     </row>
     <row r="290">
@@ -12331,7 +12331,7 @@
         <v>17</v>
       </c>
       <c r="K290" t="n">
-        <v>3.6677205878571</v>
+        <v>3.671447104625428</v>
       </c>
     </row>
     <row r="291">
@@ -12372,7 +12372,7 @@
         <v>17</v>
       </c>
       <c r="K291" t="n">
-        <v>3.641148145088365</v>
+        <v>3.645149598476893</v>
       </c>
     </row>
     <row r="292">
@@ -12413,7 +12413,7 @@
         <v>17</v>
       </c>
       <c r="K292" t="n">
-        <v>3.644153531848513</v>
+        <v>3.641573684843078</v>
       </c>
     </row>
     <row r="293">
@@ -12454,7 +12454,7 @@
         <v>17</v>
       </c>
       <c r="K293" t="n">
-        <v>3.660552290184961</v>
+        <v>3.658320621474157</v>
       </c>
     </row>
     <row r="294">
@@ -12495,7 +12495,7 @@
         <v>17</v>
       </c>
       <c r="K294" t="n">
-        <v>3.681538851213801</v>
+        <v>3.679266566237186</v>
       </c>
     </row>
     <row r="295">
@@ -12536,7 +12536,7 @@
         <v>17</v>
       </c>
       <c r="K295" t="n">
-        <v>3.684059607913598</v>
+        <v>3.685095109196796</v>
       </c>
     </row>
     <row r="296">
@@ -12577,7 +12577,7 @@
         <v>17</v>
       </c>
       <c r="K296" t="n">
-        <v>3.684059607913598</v>
+        <v>3.67065505941005</v>
       </c>
     </row>
     <row r="297">
@@ -12618,7 +12618,7 @@
         <v>17</v>
       </c>
       <c r="K297" t="n">
-        <v>3.650630805050255</v>
+        <v>3.653263275513086</v>
       </c>
     </row>
     <row r="298">
@@ -12659,7 +12659,7 @@
         <v>17</v>
       </c>
       <c r="K298" t="n">
-        <v>3.625302975125997</v>
+        <v>3.623672944631993</v>
       </c>
     </row>
     <row r="299">
@@ -12700,7 +12700,7 @@
         <v>17</v>
       </c>
       <c r="K299" t="n">
-        <v>3.625302975125997</v>
+        <v>3.623672944631993</v>
       </c>
     </row>
     <row r="300">
@@ -12741,7 +12741,7 @@
         <v>17</v>
       </c>
       <c r="K300" t="n">
-        <v>3.632853954672842</v>
+        <v>3.630122405649832</v>
       </c>
     </row>
     <row r="301">
@@ -12782,7 +12782,7 @@
         <v>17</v>
       </c>
       <c r="K301" t="n">
-        <v>3.628842497899514</v>
+        <v>3.63147638895504</v>
       </c>
     </row>
     <row r="302">
@@ -12823,7 +12823,7 @@
         <v>17</v>
       </c>
       <c r="K302" t="n">
-        <v>3.628842497899514</v>
+        <v>3.63147638895504</v>
       </c>
     </row>
     <row r="303">
@@ -12864,7 +12864,7 @@
         <v>17</v>
       </c>
       <c r="K303" t="n">
-        <v>3.549838415202781</v>
+        <v>3.559424287722149</v>
       </c>
     </row>
     <row r="304">
@@ -12905,7 +12905,7 @@
         <v>17</v>
       </c>
       <c r="K304" t="n">
-        <v>3.549838415202781</v>
+        <v>3.559424287722149</v>
       </c>
     </row>
     <row r="305">
@@ -12946,7 +12946,7 @@
         <v>17</v>
       </c>
       <c r="K305" t="n">
-        <v>3.458767526516053</v>
+        <v>3.466296212029136</v>
       </c>
     </row>
     <row r="306">
@@ -12987,7 +12987,7 @@
         <v>17</v>
       </c>
       <c r="K306" t="n">
-        <v>3.425074252277918</v>
+        <v>3.428327545514213</v>
       </c>
     </row>
     <row r="307">
@@ -13028,7 +13028,7 @@
         <v>17</v>
       </c>
       <c r="K307" t="n">
-        <v>3.425074252277918</v>
+        <v>3.425337092247305</v>
       </c>
     </row>
     <row r="308">
@@ -13069,7 +13069,7 @@
         <v>17</v>
       </c>
       <c r="K308" t="n">
-        <v>3.426569821194597</v>
+        <v>3.425337092247305</v>
       </c>
     </row>
     <row r="309">
@@ -13110,7 +13110,7 @@
         <v>17</v>
       </c>
       <c r="K309" t="n">
-        <v>3.44663052952153</v>
+        <v>3.446506578519883</v>
       </c>
     </row>
     <row r="310">
@@ -13151,7 +13151,7 @@
         <v>17</v>
       </c>
       <c r="K310" t="n">
-        <v>3.45471783450593</v>
+        <v>3.452861145218817</v>
       </c>
     </row>
     <row r="311">
@@ -13192,7 +13192,7 @@
         <v>17</v>
       </c>
       <c r="K311" t="n">
-        <v>3.465044627980021</v>
+        <v>3.464007098788308</v>
       </c>
     </row>
     <row r="312">
@@ -13233,7 +13233,7 @@
         <v>17</v>
       </c>
       <c r="K312" t="n">
-        <v>3.454341162208261</v>
+        <v>3.457122700290899</v>
       </c>
     </row>
     <row r="313">
@@ -13274,7 +13274,7 @@
         <v>17</v>
       </c>
       <c r="K313" t="n">
-        <v>3.470017217821829</v>
+        <v>3.497745947844657</v>
       </c>
     </row>
     <row r="314">
@@ -13315,7 +13315,7 @@
         <v>17</v>
       </c>
       <c r="K314" t="n">
-        <v>3.470017217821829</v>
+        <v>3.497745947844657</v>
       </c>
     </row>
     <row r="315">
@@ -13356,7 +13356,7 @@
         <v>17</v>
       </c>
       <c r="K315" t="n">
-        <v>3.470017217821829</v>
+        <v>3.497745947844657</v>
       </c>
     </row>
     <row r="316">
@@ -13397,7 +13397,7 @@
         <v>17</v>
       </c>
       <c r="K316" t="n">
-        <v>3.609334957516086</v>
+        <v>3.603248500505296</v>
       </c>
     </row>
     <row r="317">
@@ -13438,7 +13438,7 @@
         <v>17</v>
       </c>
       <c r="K317" t="n">
-        <v>3.644635090491765</v>
+        <v>3.64026587935767</v>
       </c>
     </row>
     <row r="318">
@@ -13479,7 +13479,7 @@
         <v>17</v>
       </c>
       <c r="K318" t="n">
-        <v>3.670549918934251</v>
+        <v>3.668411387488443</v>
       </c>
     </row>
     <row r="319">
@@ -13520,7 +13520,7 @@
         <v>17</v>
       </c>
       <c r="K319" t="n">
-        <v>3.689656664032654</v>
+        <v>3.689242849377008</v>
       </c>
     </row>
     <row r="320">
@@ -13561,7 +13561,7 @@
         <v>17</v>
       </c>
       <c r="K320" t="n">
-        <v>3.678599584138844</v>
+        <v>3.681323310225096</v>
       </c>
     </row>
     <row r="321">
@@ -13602,7 +13602,7 @@
         <v>17</v>
       </c>
       <c r="K321" t="n">
-        <v>3.615783108964975</v>
+        <v>3.620825780102938</v>
       </c>
     </row>
     <row r="322">
@@ -13643,7 +13643,7 @@
         <v>17</v>
       </c>
       <c r="K322" t="n">
-        <v>3.615783108964975</v>
+        <v>3.620825780102938</v>
       </c>
     </row>
     <row r="323">
@@ -13684,7 +13684,7 @@
         <v>17</v>
       </c>
       <c r="K323" t="n">
-        <v>3.442446843625275</v>
+        <v>3.45352306498394</v>
       </c>
     </row>
     <row r="324">
@@ -13725,7 +13725,7 @@
         <v>17</v>
       </c>
       <c r="K324" t="n">
-        <v>3.367238765017977</v>
+        <v>3.377038752636145</v>
       </c>
     </row>
     <row r="325">
@@ -13766,7 +13766,7 @@
         <v>17</v>
       </c>
       <c r="K325" t="n">
-        <v>3.306622050070488</v>
+        <v>3.314996710828233</v>
       </c>
     </row>
     <row r="326">
@@ -13807,7 +13807,7 @@
         <v>17</v>
       </c>
       <c r="K326" t="n">
-        <v>3.212488749534586</v>
+        <v>3.185200535456386</v>
       </c>
     </row>
     <row r="327">
@@ -13848,7 +13848,7 @@
         <v>17</v>
       </c>
       <c r="K327" t="n">
-        <v>3.179307280272579</v>
+        <v>3.185200535456386</v>
       </c>
     </row>
     <row r="328">
@@ -13889,7 +13889,7 @@
         <v>17</v>
       </c>
       <c r="K328" t="n">
-        <v>3.179307280272579</v>
+        <v>3.185200535456386</v>
       </c>
     </row>
     <row r="329">
@@ -13930,7 +13930,7 @@
         <v>17</v>
       </c>
       <c r="K329" t="n">
-        <v>3.138173059942436</v>
+        <v>3.142079524357781</v>
       </c>
     </row>
     <row r="330">
@@ -13971,7 +13971,7 @@
         <v>17</v>
       </c>
       <c r="K330" t="n">
-        <v>3.116535346191523</v>
+        <v>3.117827932129661</v>
       </c>
     </row>
     <row r="331">
@@ -14012,7 +14012,7 @@
         <v>17</v>
       </c>
       <c r="K331" t="n">
-        <v>3.104580113869082</v>
+        <v>3.106643942172711</v>
       </c>
     </row>
     <row r="332">
@@ -14053,7 +14053,7 @@
         <v>17</v>
       </c>
       <c r="K332" t="n">
-        <v>3.07672053794179</v>
+        <v>3.082550979254786</v>
       </c>
     </row>
     <row r="333">
@@ -14094,7 +14094,7 @@
         <v>17</v>
       </c>
       <c r="K333" t="n">
-        <v>2.971820668640397</v>
+        <v>2.979859977519101</v>
       </c>
     </row>
     <row r="334">
@@ -14135,7 +14135,7 @@
         <v>17</v>
       </c>
       <c r="K334" t="n">
-        <v>2.914163368059623</v>
+        <v>2.922476325965659</v>
       </c>
     </row>
     <row r="335">
@@ -14176,7 +14176,7 @@
         <v>17</v>
       </c>
       <c r="K335" t="n">
-        <v>2.914163368059623</v>
+        <v>2.922476325965659</v>
       </c>
     </row>
     <row r="336">
@@ -14217,7 +14217,7 @@
         <v>17</v>
       </c>
       <c r="K336" t="n">
-        <v>2.914163368059623</v>
+        <v>2.922476325965659</v>
       </c>
     </row>
     <row r="337">
@@ -14258,7 +14258,7 @@
         <v>17</v>
       </c>
       <c r="K337" t="n">
-        <v>2.776312386454657</v>
+        <v>2.787794139793007</v>
       </c>
     </row>
     <row r="338">
@@ -14299,7 +14299,7 @@
         <v>17</v>
       </c>
       <c r="K338" t="n">
-        <v>2.776312386454657</v>
+        <v>2.787794139793007</v>
       </c>
     </row>
     <row r="339">
@@ -14340,7 +14340,7 @@
         <v>17</v>
       </c>
       <c r="K339" t="n">
-        <v>2.620887134843976</v>
+        <v>2.632361200659081</v>
       </c>
     </row>
     <row r="340">
@@ -14381,7 +14381,7 @@
         <v>17</v>
       </c>
       <c r="K340" t="n">
-        <v>2.620887134843976</v>
+        <v>2.55080500566628</v>
       </c>
     </row>
     <row r="341">
@@ -14422,7 +14422,7 @@
         <v>17</v>
       </c>
       <c r="K341" t="n">
-        <v>2.540904816686957</v>
+        <v>2.55080500566628</v>
       </c>
     </row>
     <row r="342">
@@ -14463,7 +14463,7 @@
         <v>17</v>
       </c>
       <c r="K342" t="n">
-        <v>2.540904816686957</v>
+        <v>2.479813667947059</v>
       </c>
     </row>
     <row r="343">
@@ -14504,7 +14504,7 @@
         <v>17</v>
       </c>
       <c r="K343" t="n">
-        <v>2.471862488068957</v>
+        <v>2.479813667947059</v>
       </c>
     </row>
     <row r="344">
@@ -14545,7 +14545,7 @@
         <v>17</v>
       </c>
       <c r="K344" t="n">
-        <v>2.43027724926417</v>
+        <v>2.435770746604776</v>
       </c>
     </row>
     <row r="345">
@@ -14586,7 +14586,7 @@
         <v>17</v>
       </c>
       <c r="K345" t="n">
-        <v>2.43027724926417</v>
+        <v>2.398367967034712</v>
       </c>
     </row>
     <row r="346">
@@ -14627,7 +14627,7 @@
         <v>17</v>
       </c>
       <c r="K346" t="n">
-        <v>2.393365450240366</v>
+        <v>2.390853590727127</v>
       </c>
     </row>
     <row r="347">
@@ -14668,7 +14668,7 @@
         <v>17</v>
       </c>
       <c r="K347" t="n">
-        <v>2.393365450240366</v>
+        <v>2.411258138338735</v>
       </c>
     </row>
     <row r="348">
@@ -14709,7 +14709,7 @@
         <v>17</v>
       </c>
       <c r="K348" t="n">
-        <v>2.525787089064798</v>
+        <v>2.521142277314528</v>
       </c>
     </row>
     <row r="349">
@@ -14750,7 +14750,7 @@
         <v>17</v>
       </c>
       <c r="K349" t="n">
-        <v>2.575138924554222</v>
+        <v>2.571209509446067</v>
       </c>
     </row>
     <row r="350">
@@ -14791,7 +14791,7 @@
         <v>17</v>
       </c>
       <c r="K350" t="n">
-        <v>2.764340528571536</v>
+        <v>2.817658151962582</v>
       </c>
     </row>
     <row r="351">
@@ -14832,7 +14832,7 @@
         <v>17</v>
       </c>
       <c r="K351" t="n">
-        <v>2.825599540429749</v>
+        <v>2.817658151962582</v>
       </c>
     </row>
     <row r="352">
@@ -14873,7 +14873,7 @@
         <v>17</v>
       </c>
       <c r="K352" t="n">
-        <v>2.825599540429749</v>
+        <v>2.817658151962582</v>
       </c>
     </row>
     <row r="353">
@@ -14914,7 +14914,7 @@
         <v>17</v>
       </c>
       <c r="K353" t="n">
-        <v>2.904421415374127</v>
+        <v>2.899025652571174</v>
       </c>
     </row>
     <row r="354">
@@ -14955,7 +14955,7 @@
         <v>17</v>
       </c>
       <c r="K354" t="n">
-        <v>2.904421415374127</v>
+        <v>2.899025652571174</v>
       </c>
     </row>
     <row r="355">
@@ -14996,7 +14996,7 @@
         <v>17</v>
       </c>
       <c r="K355" t="n">
-        <v>2.904421415374127</v>
+        <v>2.922212479555804</v>
       </c>
     </row>
     <row r="356">
@@ -15037,7 +15037,7 @@
         <v>17</v>
       </c>
       <c r="K356" t="n">
-        <v>2.947504670408372</v>
+        <v>2.944578081030393</v>
       </c>
     </row>
     <row r="357">
@@ -15078,7 +15078,7 @@
         <v>17</v>
       </c>
       <c r="K357" t="n">
-        <v>2.952304731693329</v>
+        <v>2.953203460374672</v>
       </c>
     </row>
     <row r="358">
@@ -15119,7 +15119,7 @@
         <v>17</v>
       </c>
       <c r="K358" t="n">
-        <v>2.952304731693329</v>
+        <v>2.942249563386772</v>
       </c>
     </row>
     <row r="359">
@@ -15160,7 +15160,7 @@
         <v>17</v>
       </c>
       <c r="K359" t="n">
-        <v>2.920852982642561</v>
+        <v>2.920715704133497</v>
       </c>
     </row>
     <row r="360">
@@ -15201,7 +15201,7 @@
         <v>17</v>
       </c>
       <c r="K360" t="n">
-        <v>2.920852982642561</v>
+        <v>2.920715704133497</v>
       </c>
     </row>
     <row r="361">
@@ -15242,7 +15242,7 @@
         <v>17</v>
       </c>
       <c r="K361" t="n">
-        <v>2.871700749598008</v>
+        <v>2.871589957684082</v>
       </c>
     </row>
     <row r="362">
@@ -15283,7 +15283,7 @@
         <v>17</v>
       </c>
       <c r="K362" t="n">
-        <v>2.80734467233463</v>
+        <v>2.810795214383129</v>
       </c>
     </row>
     <row r="363">
@@ -15324,7 +15324,7 @@
         <v>17</v>
       </c>
       <c r="K363" t="n">
-        <v>2.80734467233463</v>
+        <v>2.810795214383129</v>
       </c>
     </row>
     <row r="364">
@@ -15365,7 +15365,7 @@
         <v>17</v>
       </c>
       <c r="K364" t="n">
-        <v>2.80734467233463</v>
+        <v>2.810795214383129</v>
       </c>
     </row>
     <row r="365">
@@ -15406,7 +15406,7 @@
         <v>17</v>
       </c>
       <c r="K365" t="n">
-        <v>2.765936029103573</v>
+        <v>2.773367053590762</v>
       </c>
     </row>
     <row r="366">
@@ -15447,7 +15447,7 @@
         <v>17</v>
       </c>
       <c r="K366" t="n">
-        <v>2.77019360229783</v>
+        <v>2.76695386634029</v>
       </c>
     </row>
     <row r="367">
@@ -15488,7 +15488,7 @@
         <v>17</v>
       </c>
       <c r="K367" t="n">
-        <v>2.787418786706317</v>
+        <v>2.78597699348296</v>
       </c>
     </row>
     <row r="368">
@@ -15529,7 +15529,7 @@
         <v>17</v>
       </c>
       <c r="K368" t="n">
-        <v>2.787418786706317</v>
+        <v>2.797642671340933</v>
       </c>
     </row>
     <row r="369">
@@ -15570,7 +15570,7 @@
         <v>17</v>
       </c>
       <c r="K369" t="n">
-        <v>2.798493270560645</v>
+        <v>2.797642671340933</v>
       </c>
     </row>
     <row r="370">
@@ -15611,7 +15611,7 @@
         <v>17</v>
       </c>
       <c r="K370" t="n">
-        <v>2.801718422390147</v>
+        <v>2.802012356738378</v>
       </c>
     </row>
     <row r="371">
@@ -15652,7 +15652,7 @@
         <v>17</v>
       </c>
       <c r="K371" t="n">
-        <v>2.770177038056914</v>
+        <v>2.770947271547625</v>
       </c>
     </row>
     <row r="372">
@@ -15693,7 +15693,7 @@
         <v>17</v>
       </c>
       <c r="K372" t="n">
-        <v>2.770177038056914</v>
+        <v>2.770947271547625</v>
       </c>
     </row>
     <row r="373">
@@ -15734,7 +15734,7 @@
         <v>17</v>
       </c>
       <c r="K373" t="n">
-        <v>2.749532216899863</v>
+        <v>2.75681497233327</v>
       </c>
     </row>
     <row r="374">
@@ -15775,7 +15775,7 @@
         <v>17</v>
       </c>
       <c r="K374" t="n">
-        <v>2.756849428593826</v>
+        <v>2.75681497233327</v>
       </c>
     </row>
     <row r="375">
@@ -15816,7 +15816,7 @@
         <v>17</v>
       </c>
       <c r="K375" t="n">
-        <v>2.744392968521497</v>
+        <v>2.747579330837835</v>
       </c>
     </row>
     <row r="376">
@@ -15857,7 +15857,7 @@
         <v>17</v>
       </c>
       <c r="K376" t="n">
-        <v>2.658993939464509</v>
+        <v>2.66007566984679</v>
       </c>
     </row>
     <row r="377">
@@ -15898,7 +15898,7 @@
         <v>17</v>
       </c>
       <c r="K377" t="n">
-        <v>2.658993939464509</v>
+        <v>2.66007566984679</v>
       </c>
     </row>
     <row r="378">
@@ -15939,7 +15939,7 @@
         <v>17</v>
       </c>
       <c r="K378" t="n">
-        <v>2.695135919964012</v>
+        <v>2.692015751845144</v>
       </c>
     </row>
     <row r="379">
@@ -15980,7 +15980,7 @@
         <v>17</v>
       </c>
       <c r="K379" t="n">
-        <v>2.726157854477671</v>
+        <v>2.722031777608582</v>
       </c>
     </row>
     <row r="380">
@@ -16021,7 +16021,7 @@
         <v>17</v>
       </c>
       <c r="K380" t="n">
-        <v>2.801207049839008</v>
+        <v>2.799665603860415</v>
       </c>
     </row>
     <row r="381">
@@ -16062,7 +16062,7 @@
         <v>17</v>
       </c>
       <c r="K381" t="n">
-        <v>2.809663611469746</v>
+        <v>2.810504051513645</v>
       </c>
     </row>
     <row r="382">
@@ -16103,7 +16103,7 @@
         <v>17</v>
       </c>
       <c r="K382" t="n">
-        <v>2.775013733819919</v>
+        <v>2.77790482581246</v>
       </c>
     </row>
     <row r="383">
@@ -16144,7 +16144,7 @@
         <v>17</v>
       </c>
       <c r="K383" t="n">
-        <v>2.765912510392572</v>
+        <v>2.766732991778653</v>
       </c>
     </row>
     <row r="384">
@@ -16185,7 +16185,7 @@
         <v>17</v>
       </c>
       <c r="K384" t="n">
-        <v>2.763541085269276</v>
+        <v>2.763563887315997</v>
       </c>
     </row>
     <row r="385">
@@ -16226,7 +16226,7 @@
         <v>17</v>
       </c>
       <c r="K385" t="n">
-        <v>2.805996940923778</v>
+        <v>2.80203991096971</v>
       </c>
     </row>
     <row r="386">
@@ -16267,7 +16267,7 @@
         <v>17</v>
       </c>
       <c r="K386" t="n">
-        <v>2.851741853822085</v>
+        <v>2.850228529634173</v>
       </c>
     </row>
     <row r="387">
@@ -16308,7 +16308,7 @@
         <v>17</v>
       </c>
       <c r="K387" t="n">
-        <v>2.905294476542439</v>
+        <v>2.898275565316509</v>
       </c>
     </row>
     <row r="388">
@@ -16349,7 +16349,7 @@
         <v>17</v>
       </c>
       <c r="K388" t="n">
-        <v>3.005192177452799</v>
+        <v>2.998573378442631</v>
       </c>
     </row>
     <row r="389">
@@ -16390,7 +16390,7 @@
         <v>17</v>
       </c>
       <c r="K389" t="n">
-        <v>3.184610483898572</v>
+        <v>3.176228171999563</v>
       </c>
     </row>
     <row r="390">
@@ -16431,7 +16431,7 @@
         <v>17</v>
       </c>
       <c r="K390" t="n">
-        <v>3.184610483898572</v>
+        <v>3.176228171999563</v>
       </c>
     </row>
     <row r="391">
@@ -16472,7 +16472,7 @@
         <v>17</v>
       </c>
       <c r="K391" t="n">
-        <v>3.243615628082315</v>
+        <v>3.235809969085063</v>
       </c>
     </row>
     <row r="392">
@@ -16513,7 +16513,7 @@
         <v>17</v>
       </c>
       <c r="K392" t="n">
-        <v>3.243615628082315</v>
+        <v>3.235809969085063</v>
       </c>
     </row>
     <row r="393">
@@ -16554,7 +16554,7 @@
         <v>17</v>
       </c>
       <c r="K393" t="n">
-        <v>3.243615628082315</v>
+        <v>3.301851015048717</v>
       </c>
     </row>
     <row r="394">
@@ -16595,7 +16595,7 @@
         <v>17</v>
       </c>
       <c r="K394" t="n">
-        <v>3.382049513275291</v>
+        <v>3.372027216269743</v>
       </c>
     </row>
     <row r="395">
@@ -16636,7 +16636,7 @@
         <v>17</v>
       </c>
       <c r="K395" t="n">
-        <v>3.538428521228544</v>
+        <v>3.528829983722021</v>
       </c>
     </row>
     <row r="396">
@@ -16677,7 +16677,7 @@
         <v>17</v>
       </c>
       <c r="K396" t="n">
-        <v>3.593799872229984</v>
+        <v>3.588853322346312</v>
       </c>
     </row>
     <row r="397">
@@ -16718,7 +16718,7 @@
         <v>17</v>
       </c>
       <c r="K397" t="n">
-        <v>3.660027777909227</v>
+        <v>3.661588635383943</v>
       </c>
     </row>
     <row r="398">
@@ -16759,7 +16759,7 @@
         <v>17</v>
       </c>
       <c r="K398" t="n">
-        <v>3.61507171300864</v>
+        <v>3.627814564031292</v>
       </c>
     </row>
     <row r="399">
@@ -16800,7 +16800,7 @@
         <v>17</v>
       </c>
       <c r="K399" t="n">
-        <v>3.671173860715732</v>
+        <v>3.668794826576177</v>
       </c>
     </row>
     <row r="400">
@@ -16841,7 +16841,7 @@
         <v>17</v>
       </c>
       <c r="K400" t="n">
-        <v>3.710390707774011</v>
+        <v>3.706727766194704</v>
       </c>
     </row>
     <row r="401">
@@ -16882,7 +16882,7 @@
         <v>17</v>
       </c>
       <c r="K401" t="n">
-        <v>3.710390707774011</v>
+        <v>3.736521854570472</v>
       </c>
     </row>
     <row r="402">
@@ -16923,7 +16923,7 @@
         <v>17</v>
       </c>
       <c r="K402" t="n">
-        <v>3.710390707774011</v>
+        <v>3.736521854570472</v>
       </c>
     </row>
     <row r="403">
@@ -16964,7 +16964,7 @@
         <v>17</v>
       </c>
       <c r="K403" t="n">
-        <v>3.780534274676064</v>
+        <v>3.782619501581051</v>
       </c>
     </row>
     <row r="404">
@@ -17005,7 +17005,7 @@
         <v>17</v>
       </c>
       <c r="K404" t="n">
-        <v>3.795604918257734</v>
+        <v>3.795405293910188</v>
       </c>
     </row>
     <row r="405">
@@ -17046,7 +17046,7 @@
         <v>17</v>
       </c>
       <c r="K405" t="n">
-        <v>3.801419868851102</v>
+        <v>3.798669697396659</v>
       </c>
     </row>
     <row r="406">
@@ -17087,7 +17087,7 @@
         <v>17</v>
       </c>
       <c r="K406" t="n">
-        <v>3.929797817388367</v>
+        <v>3.924539696163019</v>
       </c>
     </row>
     <row r="407">
@@ -17128,7 +17128,7 @@
         <v>17</v>
       </c>
       <c r="K407" t="n">
-        <v>3.964348551067588</v>
+        <v>3.96018733104379</v>
       </c>
     </row>
     <row r="408">
@@ -17169,7 +17169,7 @@
         <v>17</v>
       </c>
       <c r="K408" t="n">
-        <v>3.997452689360506</v>
+        <v>3.993869998720048</v>
       </c>
     </row>
     <row r="409">
@@ -17210,7 +17210,7 @@
         <v>17</v>
       </c>
       <c r="K409" t="n">
-        <v>3.997452689360506</v>
+        <v>3.993869998720048</v>
       </c>
     </row>
     <row r="410">
@@ -17251,7 +17251,7 @@
         <v>17</v>
       </c>
       <c r="K410" t="n">
-        <v>3.997452689360506</v>
+        <v>3.993869998720048</v>
       </c>
     </row>
     <row r="411">
@@ -17292,7 +17292,7 @@
         <v>17</v>
       </c>
       <c r="K411" t="n">
-        <v>4.083029266622431</v>
+        <v>4.081046294361964</v>
       </c>
     </row>
     <row r="412">
@@ -17333,7 +17333,7 @@
         <v>17</v>
       </c>
       <c r="K412" t="n">
-        <v>4.083029266622431</v>
+        <v>4.081046294361964</v>
       </c>
     </row>
     <row r="413">
@@ -17374,7 +17374,7 @@
         <v>17</v>
       </c>
       <c r="K413" t="n">
-        <v>4.087139924264963</v>
+        <v>4.088569843639695</v>
       </c>
     </row>
     <row r="414">
@@ -17415,7 +17415,7 @@
         <v>17</v>
       </c>
       <c r="K414" t="n">
-        <v>4.072234252418417</v>
+        <v>4.074529957317241</v>
       </c>
     </row>
     <row r="415">
@@ -17456,7 +17456,7 @@
         <v>17</v>
       </c>
       <c r="K415" t="n">
-        <v>4.072234252418417</v>
+        <v>4.074529957317241</v>
       </c>
     </row>
     <row r="416">
@@ -17497,7 +17497,7 @@
         <v>17</v>
       </c>
       <c r="K416" t="n">
-        <v>4.044022780639918</v>
+        <v>4.048329148961807</v>
       </c>
     </row>
     <row r="417">
@@ -17538,7 +17538,7 @@
         <v>17</v>
       </c>
       <c r="K417" t="n">
-        <v>3.928399375433863</v>
+        <v>3.937243837098535</v>
       </c>
     </row>
     <row r="418">
@@ -17579,7 +17579,7 @@
         <v>17</v>
       </c>
       <c r="K418" t="n">
-        <v>3.79282952964617</v>
+        <v>3.801157543035595</v>
       </c>
     </row>
     <row r="419">
@@ -17620,7 +17620,7 @@
         <v>17</v>
       </c>
       <c r="K419" t="n">
-        <v>3.667896814661319</v>
+        <v>3.674071502284283</v>
       </c>
     </row>
     <row r="420">
@@ -17661,7 +17661,7 @@
         <v>17</v>
       </c>
       <c r="K420" t="n">
-        <v>3.594897740078386</v>
+        <v>3.597573928859939</v>
       </c>
     </row>
     <row r="421">
@@ -17702,7 +17702,7 @@
         <v>17</v>
       </c>
       <c r="K421" t="n">
-        <v>3.576293119169515</v>
+        <v>3.578470298195148</v>
       </c>
     </row>
     <row r="422">
@@ -17743,7 +17743,7 @@
         <v>17</v>
       </c>
       <c r="K422" t="n">
-        <v>3.541535421219214</v>
+        <v>3.540417378983467</v>
       </c>
     </row>
     <row r="423">
@@ -17784,7 +17784,7 @@
         <v>17</v>
       </c>
       <c r="K423" t="n">
-        <v>3.587984362972594</v>
+        <v>3.583500754647436</v>
       </c>
     </row>
     <row r="424">
@@ -17825,7 +17825,7 @@
         <v>17</v>
       </c>
       <c r="K424" t="n">
-        <v>3.645236461662936</v>
+        <v>3.634789601170894</v>
       </c>
     </row>
     <row r="425">
@@ -17866,7 +17866,7 @@
         <v>17</v>
       </c>
       <c r="K425" t="n">
-        <v>3.727144467722978</v>
+        <v>3.719045552772769</v>
       </c>
     </row>
     <row r="426">
@@ -17907,7 +17907,7 @@
         <v>17</v>
       </c>
       <c r="K426" t="n">
-        <v>3.75604236616257</v>
+        <v>3.750961391197083</v>
       </c>
     </row>
     <row r="427">
@@ -17948,7 +17948,7 @@
         <v>17</v>
       </c>
       <c r="K427" t="n">
-        <v>3.75604236616257</v>
+        <v>3.750961391197083</v>
       </c>
     </row>
     <row r="428">
@@ -17989,7 +17989,7 @@
         <v>17</v>
       </c>
       <c r="K428" t="n">
-        <v>3.75604236616257</v>
+        <v>3.750961391197083</v>
       </c>
     </row>
     <row r="429">
@@ -18030,7 +18030,7 @@
         <v>17</v>
       </c>
       <c r="K429" t="n">
-        <v>3.781634202389674</v>
+        <v>3.782227176355607</v>
       </c>
     </row>
     <row r="430">
@@ -18071,7 +18071,7 @@
         <v>17</v>
       </c>
       <c r="K430" t="n">
-        <v>3.65605471131486</v>
+        <v>3.556729382715019</v>
       </c>
     </row>
     <row r="431">
@@ -18112,7 +18112,7 @@
         <v>17</v>
       </c>
       <c r="K431" t="n">
-        <v>3.542396267105798</v>
+        <v>3.556729382715019</v>
       </c>
     </row>
     <row r="432">
@@ -18153,7 +18153,7 @@
         <v>17</v>
       </c>
       <c r="K432" t="n">
-        <v>3.141378059402435</v>
+        <v>3.155392938956257</v>
       </c>
     </row>
     <row r="433">
@@ -18194,7 +18194,7 @@
         <v>17</v>
       </c>
       <c r="K433" t="n">
-        <v>3.026591975839695</v>
+        <v>3.040935413887297</v>
       </c>
     </row>
     <row r="434">
@@ -18235,7 +18235,7 @@
         <v>17</v>
       </c>
       <c r="K434" t="n">
-        <v>2.905565662175724</v>
+        <v>2.91981353479499</v>
       </c>
     </row>
     <row r="435">
@@ -18276,7 +18276,7 @@
         <v>17</v>
       </c>
       <c r="K435" t="n">
-        <v>2.764443716439859</v>
+        <v>2.762899115536035</v>
       </c>
     </row>
     <row r="436">
@@ -18317,7 +18317,7 @@
         <v>17</v>
       </c>
       <c r="K436" t="n">
-        <v>2.870800376996876</v>
+        <v>2.862949240233238</v>
       </c>
     </row>
     <row r="437">
@@ -18358,7 +18358,7 @@
         <v>17</v>
       </c>
       <c r="K437" t="n">
-        <v>2.991703632784143</v>
+        <v>2.989907593443225</v>
       </c>
     </row>
     <row r="438">
@@ -18399,7 +18399,7 @@
         <v>17</v>
       </c>
       <c r="K438" t="n">
-        <v>2.991703632784143</v>
+        <v>2.989907593443225</v>
       </c>
     </row>
     <row r="439">
@@ -18440,7 +18440,7 @@
         <v>17</v>
       </c>
       <c r="K439" t="n">
-        <v>3.051650993000666</v>
+        <v>3.048877486837218</v>
       </c>
     </row>
     <row r="440">
@@ -18481,7 +18481,7 @@
         <v>17</v>
       </c>
       <c r="K440" t="n">
-        <v>3.147139198886634</v>
+        <v>3.142578702725303</v>
       </c>
     </row>
     <row r="441">
@@ -18522,7 +18522,7 @@
         <v>17</v>
       </c>
       <c r="K441" t="n">
-        <v>3.174036452472641</v>
+        <v>3.171631218861926</v>
       </c>
     </row>
     <row r="442">
@@ -18563,7 +18563,7 @@
         <v>17</v>
       </c>
       <c r="K442" t="n">
-        <v>3.174036452472641</v>
+        <v>3.187082123928092</v>
       </c>
     </row>
     <row r="443">
@@ -18604,7 +18604,7 @@
         <v>17</v>
       </c>
       <c r="K443" t="n">
-        <v>3.255851323750111</v>
+        <v>3.25371806104438</v>
       </c>
     </row>
     <row r="444">
@@ -18645,7 +18645,7 @@
         <v>17</v>
       </c>
       <c r="K444" t="n">
-        <v>3.270372675824166</v>
+        <v>3.269287078036533</v>
       </c>
     </row>
     <row r="445">
@@ -18686,7 +18686,7 @@
         <v>17</v>
       </c>
       <c r="K445" t="n">
-        <v>3.270372675824166</v>
+        <v>3.269287078036533</v>
       </c>
     </row>
     <row r="446">
@@ -18727,7 +18727,7 @@
         <v>17</v>
       </c>
       <c r="K446" t="n">
-        <v>3.270372675824166</v>
+        <v>3.269287078036533</v>
       </c>
     </row>
     <row r="447">
@@ -18768,7 +18768,7 @@
         <v>17</v>
       </c>
       <c r="K447" t="n">
-        <v>3.290069851237608</v>
+        <v>3.288712044144317</v>
       </c>
     </row>
     <row r="448">
@@ -18809,7 +18809,7 @@
         <v>17</v>
       </c>
       <c r="K448" t="n">
-        <v>3.323761741150804</v>
+        <v>3.322609444278499</v>
       </c>
     </row>
     <row r="449">
@@ -18850,7 +18850,7 @@
         <v>17</v>
       </c>
       <c r="K449" t="n">
-        <v>3.352676467186824</v>
+        <v>3.349188157125164</v>
       </c>
     </row>
     <row r="450">
@@ -18891,7 +18891,7 @@
         <v>17</v>
       </c>
       <c r="K450" t="n">
-        <v>3.416958203107772</v>
+        <v>3.416672284665728</v>
       </c>
     </row>
     <row r="451">
@@ -18932,7 +18932,7 @@
         <v>17</v>
       </c>
       <c r="K451" t="n">
-        <v>3.416958203107772</v>
+        <v>3.416672284665728</v>
       </c>
     </row>
     <row r="452">
@@ -18973,7 +18973,7 @@
         <v>17</v>
       </c>
       <c r="K452" t="n">
-        <v>3.416958203107772</v>
+        <v>3.416672284665728</v>
       </c>
     </row>
     <row r="453">
@@ -19014,7 +19014,7 @@
         <v>17</v>
       </c>
       <c r="K453" t="n">
-        <v>3.413257939186639</v>
+        <v>3.413449100181562</v>
       </c>
     </row>
     <row r="454">
@@ -19055,7 +19055,7 @@
         <v>17</v>
       </c>
       <c r="K454" t="n">
-        <v>3.387291927027757</v>
+        <v>3.388412778320694</v>
       </c>
     </row>
     <row r="455">
@@ -19096,7 +19096,7 @@
         <v>17</v>
       </c>
       <c r="K455" t="n">
-        <v>3.375666279812209</v>
+        <v>3.375704781485822</v>
       </c>
     </row>
     <row r="456">
@@ -19137,7 +19137,7 @@
         <v>17</v>
       </c>
       <c r="K456" t="n">
-        <v>3.370563414970764</v>
+        <v>3.371588415802593</v>
       </c>
     </row>
     <row r="457">
@@ -19178,7 +19178,7 @@
         <v>17</v>
       </c>
       <c r="K457" t="n">
-        <v>3.332650081332778</v>
+        <v>3.334352793499364</v>
       </c>
     </row>
     <row r="458">
@@ -19219,7 +19219,7 @@
         <v>17</v>
       </c>
       <c r="K458" t="n">
-        <v>3.332650081332778</v>
+        <v>3.334352793499364</v>
       </c>
     </row>
     <row r="459">
@@ -19260,7 +19260,7 @@
         <v>17</v>
       </c>
       <c r="K459" t="n">
-        <v>3.307618122815602</v>
+        <v>3.3086940443667</v>
       </c>
     </row>
     <row r="460">
@@ -19301,7 +19301,7 @@
         <v>17</v>
       </c>
       <c r="K460" t="n">
-        <v>3.307618122815602</v>
+        <v>3.3086940443667</v>
       </c>
     </row>
     <row r="461">
@@ -19342,7 +19342,7 @@
         <v>17</v>
       </c>
       <c r="K461" t="n">
-        <v>3.309710866086844</v>
+        <v>3.308589821121926</v>
       </c>
     </row>
     <row r="462">
@@ -19383,7 +19383,7 @@
         <v>17</v>
       </c>
       <c r="K462" t="n">
-        <v>3.328727906246722</v>
+        <v>3.326902342444458</v>
       </c>
     </row>
     <row r="463">
@@ -19424,7 +19424,7 @@
         <v>17</v>
       </c>
       <c r="K463" t="n">
-        <v>3.326277438556393</v>
+        <v>3.326902342444458</v>
       </c>
     </row>
     <row r="464">
@@ -19465,7 +19465,7 @@
         <v>17</v>
       </c>
       <c r="K464" t="n">
-        <v>3.326277438556393</v>
+        <v>3.326902342444458</v>
       </c>
     </row>
     <row r="465">
@@ -19506,7 +19506,7 @@
         <v>17</v>
       </c>
       <c r="K465" t="n">
-        <v>3.291251117876924</v>
+        <v>3.265166323247071</v>
       </c>
     </row>
     <row r="466">
@@ -19547,7 +19547,7 @@
         <v>17</v>
       </c>
       <c r="K466" t="n">
-        <v>3.22076134866522</v>
+        <v>3.225534127625883</v>
       </c>
     </row>
     <row r="467">
@@ -19588,7 +19588,7 @@
         <v>17</v>
       </c>
       <c r="K467" t="n">
-        <v>3.14223165309732</v>
+        <v>3.143144557225391</v>
       </c>
     </row>
     <row r="468">
@@ -19629,7 +19629,7 @@
         <v>17</v>
       </c>
       <c r="K468" t="n">
-        <v>3.142399682621516</v>
+        <v>3.142295268985003</v>
       </c>
     </row>
     <row r="469">
@@ -19670,7 +19670,7 @@
         <v>17</v>
       </c>
       <c r="K469" t="n">
-        <v>3.200123019617743</v>
+        <v>3.196488995514073</v>
       </c>
     </row>
     <row r="470">
@@ -19711,7 +19711,7 @@
         <v>17</v>
       </c>
       <c r="K470" t="n">
-        <v>3.235013145144753</v>
+        <v>3.230805449661702</v>
       </c>
     </row>
     <row r="471">
@@ -19752,7 +19752,7 @@
         <v>17</v>
       </c>
       <c r="K471" t="n">
-        <v>3.396401123982606</v>
+        <v>3.390475666927869</v>
       </c>
     </row>
     <row r="472">
@@ -19793,7 +19793,7 @@
         <v>17</v>
       </c>
       <c r="K472" t="n">
-        <v>3.442488361839911</v>
+        <v>3.437781244498451</v>
       </c>
     </row>
     <row r="473">
@@ -19834,7 +19834,7 @@
         <v>17</v>
       </c>
       <c r="K473" t="n">
-        <v>3.49200128413723</v>
+        <v>3.50790015725514</v>
       </c>
     </row>
     <row r="474">
@@ -19875,7 +19875,7 @@
         <v>17</v>
       </c>
       <c r="K474" t="n">
-        <v>3.509741654878422</v>
+        <v>3.50790015725514</v>
       </c>
     </row>
     <row r="475">
@@ -19916,7 +19916,7 @@
         <v>17</v>
       </c>
       <c r="K475" t="n">
-        <v>3.512733756813813</v>
+        <v>3.515641964808179</v>
       </c>
     </row>
     <row r="476">
@@ -19957,7 +19957,7 @@
         <v>17</v>
       </c>
       <c r="K476" t="n">
-        <v>3.446489899919444</v>
+        <v>3.451013763594342</v>
       </c>
     </row>
     <row r="477">
@@ -19998,7 +19998,7 @@
         <v>17</v>
       </c>
       <c r="K477" t="n">
-        <v>3.405114739111695</v>
+        <v>3.409952532179544</v>
       </c>
     </row>
     <row r="478">
@@ -20039,7 +20039,7 @@
         <v>17</v>
       </c>
       <c r="K478" t="n">
-        <v>3.356868993517409</v>
+        <v>3.36329357885992</v>
       </c>
     </row>
     <row r="479">
@@ -20080,7 +20080,7 @@
         <v>17</v>
       </c>
       <c r="K479" t="n">
-        <v>3.225858666887824</v>
+        <v>3.232108270736212</v>
       </c>
     </row>
     <row r="480">
@@ -20121,7 +20121,7 @@
         <v>17</v>
       </c>
       <c r="K480" t="n">
-        <v>3.192826584565431</v>
+        <v>3.195291722733069</v>
       </c>
     </row>
     <row r="481">
@@ -20162,7 +20162,7 @@
         <v>17</v>
       </c>
       <c r="K481" t="n">
-        <v>3.168269231333538</v>
+        <v>3.171622983952938</v>
       </c>
     </row>
     <row r="482">
@@ -20203,7 +20203,7 @@
         <v>17</v>
       </c>
       <c r="K482" t="n">
-        <v>3.104387859555989</v>
+        <v>3.104243440299044</v>
       </c>
     </row>
     <row r="483">
@@ -20244,7 +20244,7 @@
         <v>17</v>
       </c>
       <c r="K483" t="n">
-        <v>3.104209467107441</v>
+        <v>3.1028520053142</v>
       </c>
     </row>
     <row r="484">
@@ -20285,7 +20285,7 @@
         <v>17</v>
       </c>
       <c r="K484" t="n">
-        <v>3.120026535097832</v>
+        <v>3.118454280169425</v>
       </c>
     </row>
     <row r="485">
@@ -20326,7 +20326,7 @@
         <v>17</v>
       </c>
       <c r="K485" t="n">
-        <v>3.144205536528029</v>
+        <v>3.143020595798788</v>
       </c>
     </row>
     <row r="486">
@@ -20367,7 +20367,7 @@
         <v>17</v>
       </c>
       <c r="K486" t="n">
-        <v>3.148552026679506</v>
+        <v>3.162149260830101</v>
       </c>
     </row>
     <row r="487">
@@ -20408,7 +20408,7 @@
         <v>17</v>
       </c>
       <c r="K487" t="n">
-        <v>3.202034142265158</v>
+        <v>3.200887088421068</v>
       </c>
     </row>
     <row r="488">
@@ -20449,7 +20449,7 @@
         <v>17</v>
       </c>
       <c r="K488" t="n">
-        <v>3.202034142265158</v>
+        <v>3.205523483487496</v>
       </c>
     </row>
     <row r="489">
@@ -20490,7 +20490,7 @@
         <v>17</v>
       </c>
       <c r="K489" t="n">
-        <v>3.202034142265158</v>
+        <v>3.205523483487496</v>
       </c>
     </row>
     <row r="490">
@@ -20531,7 +20531,7 @@
         <v>17</v>
       </c>
       <c r="K490" t="n">
-        <v>3.19912490803624</v>
+        <v>3.199316277851729</v>
       </c>
     </row>
     <row r="491">
@@ -20572,7 +20572,7 @@
         <v>17</v>
       </c>
       <c r="K491" t="n">
-        <v>3.19912490803624</v>
+        <v>3.199316277851729</v>
       </c>
     </row>
     <row r="492">
@@ -20613,7 +20613,7 @@
         <v>17</v>
       </c>
       <c r="K492" t="n">
-        <v>3.135609901453869</v>
+        <v>3.14161740977026</v>
       </c>
     </row>
     <row r="493">
@@ -20654,7 +20654,7 @@
         <v>17</v>
       </c>
       <c r="K493" t="n">
-        <v>3.135609901453869</v>
+        <v>3.098713251455035</v>
       </c>
     </row>
     <row r="494">
@@ -20695,7 +20695,7 @@
         <v>17</v>
       </c>
       <c r="K494" t="n">
-        <v>3.135609901453869</v>
+        <v>3.098713251455035</v>
       </c>
     </row>
     <row r="495">
@@ -20736,7 +20736,7 @@
         <v>17</v>
       </c>
       <c r="K495" t="n">
-        <v>3.099324435648891</v>
+        <v>3.098713251455035</v>
       </c>
     </row>
     <row r="496">
@@ -20777,7 +20777,7 @@
         <v>17</v>
       </c>
       <c r="K496" t="n">
-        <v>3.099324435648891</v>
+        <v>3.098713251455035</v>
       </c>
     </row>
     <row r="497">
@@ -20818,7 +20818,7 @@
         <v>17</v>
       </c>
       <c r="K497" t="n">
-        <v>3.099324435648891</v>
+        <v>3.064767826809912</v>
       </c>
     </row>
     <row r="498">
@@ -20859,7 +20859,7 @@
         <v>17</v>
       </c>
       <c r="K498" t="n">
-        <v>2.9863796296173</v>
+        <v>2.985556917958172</v>
       </c>
     </row>
     <row r="499">
@@ -20900,7 +20900,7 @@
         <v>17</v>
       </c>
       <c r="K499" t="n">
-        <v>2.999404938429786</v>
+        <v>2.998474841689534</v>
       </c>
     </row>
     <row r="500">
@@ -20941,7 +20941,7 @@
         <v>17</v>
       </c>
       <c r="K500" t="n">
-        <v>3.009284555274396</v>
+        <v>3.007549989817059</v>
       </c>
     </row>
     <row r="501">
@@ -20982,7 +20982,7 @@
         <v>17</v>
       </c>
       <c r="K501" t="n">
-        <v>3.081316715585285</v>
+        <v>3.079638816437898</v>
       </c>
     </row>
     <row r="502">
@@ -21023,7 +21023,7 @@
         <v>17</v>
       </c>
       <c r="K502" t="n">
-        <v>3.081316715585285</v>
+        <v>3.079638816437898</v>
       </c>
     </row>
     <row r="503">
@@ -21064,7 +21064,7 @@
         <v>17</v>
       </c>
       <c r="K503" t="n">
-        <v>3.106071662106237</v>
+        <v>3.1050407118353</v>
       </c>
     </row>
     <row r="504">
@@ -21105,7 +21105,7 @@
         <v>17</v>
       </c>
       <c r="K504" t="n">
-        <v>3.106071662106237</v>
+        <v>3.1050407118353</v>
       </c>
     </row>
     <row r="505">
@@ -21146,7 +21146,7 @@
         <v>17</v>
       </c>
       <c r="K505" t="n">
-        <v>3.090109123322163</v>
+        <v>3.094483691026719</v>
       </c>
     </row>
     <row r="506">
@@ -21187,7 +21187,7 @@
         <v>17</v>
       </c>
       <c r="K506" t="n">
-        <v>3.090109123322163</v>
+        <v>3.094483691026719</v>
       </c>
     </row>
     <row r="507">
@@ -21228,7 +21228,7 @@
         <v>17</v>
       </c>
       <c r="K507" t="n">
-        <v>3.090109123322163</v>
+        <v>3.094483691026719</v>
       </c>
     </row>
     <row r="508">
@@ -21269,7 +21269,7 @@
         <v>17</v>
       </c>
       <c r="K508" t="n">
-        <v>3.039451314681903</v>
+        <v>3.046053108867909</v>
       </c>
     </row>
     <row r="509">
@@ -21310,7 +21310,7 @@
         <v>17</v>
       </c>
       <c r="K509" t="n">
-        <v>2.910725535245783</v>
+        <v>2.86284121147309</v>
       </c>
     </row>
     <row r="510">
@@ -21351,7 +21351,7 @@
         <v>17</v>
       </c>
       <c r="K510" t="n">
-        <v>2.85707601317548</v>
+        <v>2.86284121147309</v>
       </c>
     </row>
     <row r="511">
@@ -21392,7 +21392,7 @@
         <v>17</v>
       </c>
       <c r="K511" t="n">
-        <v>2.738726360801794</v>
+        <v>2.74569268052965</v>
       </c>
     </row>
     <row r="512">
@@ -21433,7 +21433,7 @@
         <v>17</v>
       </c>
       <c r="K512" t="n">
-        <v>2.642295402350769</v>
+        <v>2.602611299346319</v>
       </c>
     </row>
     <row r="513">
@@ -21474,7 +21474,7 @@
         <v>17</v>
       </c>
       <c r="K513" t="n">
-        <v>2.596704838889969</v>
+        <v>2.602611299346319</v>
       </c>
     </row>
     <row r="514">
@@ -21515,7 +21515,7 @@
         <v>17</v>
       </c>
       <c r="K514" t="n">
-        <v>2.596704838889969</v>
+        <v>2.602611299346319</v>
       </c>
     </row>
     <row r="515">
@@ -21556,7 +21556,7 @@
         <v>17</v>
       </c>
       <c r="K515" t="n">
-        <v>2.596704838889969</v>
+        <v>2.602611299346319</v>
       </c>
     </row>
     <row r="516">
@@ -21597,7 +21597,7 @@
         <v>17</v>
       </c>
       <c r="K516" t="n">
-        <v>2.461398074046292</v>
+        <v>2.46848377076032</v>
       </c>
     </row>
     <row r="517">
@@ -21638,7 +21638,7 @@
         <v>17</v>
       </c>
       <c r="K517" t="n">
-        <v>2.402575438606732</v>
+        <v>2.40840361357775</v>
       </c>
     </row>
     <row r="518">
@@ -21679,7 +21679,7 @@
         <v>17</v>
       </c>
       <c r="K518" t="n">
-        <v>2.360552220828187</v>
+        <v>2.364292850093205</v>
       </c>
     </row>
     <row r="519">
@@ -21720,7 +21720,7 @@
         <v>17</v>
       </c>
       <c r="K519" t="n">
-        <v>2.360552220828187</v>
+        <v>2.364292850093205</v>
       </c>
     </row>
     <row r="520">
@@ -21761,7 +21761,7 @@
         <v>17</v>
       </c>
       <c r="K520" t="n">
-        <v>2.300129693811184</v>
+        <v>2.298659483462532</v>
       </c>
     </row>
     <row r="521">
@@ -21802,7 +21802,7 @@
         <v>17</v>
       </c>
       <c r="K521" t="n">
-        <v>2.300129693811184</v>
+        <v>2.298659483462532</v>
       </c>
     </row>
     <row r="522">
@@ -21843,7 +21843,7 @@
         <v>17</v>
       </c>
       <c r="K522" t="n">
-        <v>2.348281614616147</v>
+        <v>2.345101136836508</v>
       </c>
     </row>
     <row r="523">
@@ -21884,7 +21884,7 @@
         <v>17</v>
       </c>
       <c r="K523" t="n">
-        <v>2.403852873999698</v>
+        <v>2.400819325094427</v>
       </c>
     </row>
     <row r="524">
@@ -21925,7 +21925,7 @@
         <v>17</v>
       </c>
       <c r="K524" t="n">
-        <v>2.449931248154544</v>
+        <v>2.447700721776116</v>
       </c>
     </row>
     <row r="525">
@@ -21966,7 +21966,7 @@
         <v>17</v>
       </c>
       <c r="K525" t="n">
-        <v>2.449931248154544</v>
+        <v>2.447700721776116</v>
       </c>
     </row>
     <row r="526">
@@ -22007,7 +22007,7 @@
         <v>17</v>
       </c>
       <c r="K526" t="n">
-        <v>2.468372662819108</v>
+        <v>2.466578747267031</v>
       </c>
     </row>
     <row r="527">
@@ -22048,7 +22048,7 @@
         <v>17</v>
       </c>
       <c r="K527" t="n">
-        <v>2.490028984394973</v>
+        <v>2.489628119937536</v>
       </c>
     </row>
     <row r="528">
@@ -22089,7 +22089,7 @@
         <v>17</v>
       </c>
       <c r="K528" t="n">
-        <v>2.490028984394973</v>
+        <v>2.489628119937536</v>
       </c>
     </row>
     <row r="529">
@@ -22130,7 +22130,7 @@
         <v>17</v>
       </c>
       <c r="K529" t="n">
-        <v>2.492874192043625</v>
+        <v>2.492475784641068</v>
       </c>
     </row>
     <row r="530">
@@ -22171,7 +22171,7 @@
         <v>17</v>
       </c>
       <c r="K530" t="n">
-        <v>2.516992670895688</v>
+        <v>2.516395195230182</v>
       </c>
     </row>
     <row r="531">
@@ -22212,7 +22212,7 @@
         <v>17</v>
       </c>
       <c r="K531" t="n">
-        <v>2.516992670895688</v>
+        <v>2.517859173558271</v>
       </c>
     </row>
     <row r="532">
@@ -22253,7 +22253,7 @@
         <v>17</v>
       </c>
       <c r="K532" t="n">
-        <v>2.517865908607768</v>
+        <v>2.517859173558271</v>
       </c>
     </row>
     <row r="533">
@@ -22294,7 +22294,7 @@
         <v>17</v>
       </c>
       <c r="K533" t="n">
-        <v>2.530095596908925</v>
+        <v>2.529167096136284</v>
       </c>
     </row>
     <row r="534">
@@ -22335,7 +22335,7 @@
         <v>17</v>
       </c>
       <c r="K534" t="n">
-        <v>2.543845783011415</v>
+        <v>2.542247468591544</v>
       </c>
     </row>
     <row r="535">
@@ -22376,7 +22376,7 @@
         <v>17</v>
       </c>
       <c r="K535" t="n">
-        <v>2.628577036886774</v>
+        <v>2.625301235932745</v>
       </c>
     </row>
     <row r="536">
@@ -22417,7 +22417,7 @@
         <v>17</v>
       </c>
       <c r="K536" t="n">
-        <v>2.65502088813278</v>
+        <v>2.652334937289883</v>
       </c>
     </row>
     <row r="537">
@@ -22458,7 +22458,7 @@
         <v>17</v>
       </c>
       <c r="K537" t="n">
-        <v>2.701683274696253</v>
+        <v>2.697103117589953</v>
       </c>
     </row>
     <row r="538">
@@ -22499,7 +22499,7 @@
         <v>17</v>
       </c>
       <c r="K538" t="n">
-        <v>2.745503747093711</v>
+        <v>2.741441246508709</v>
       </c>
     </row>
     <row r="539">
@@ -22540,7 +22540,7 @@
         <v>17</v>
       </c>
       <c r="K539" t="n">
-        <v>2.870154078329892</v>
+        <v>2.866706334414398</v>
       </c>
     </row>
     <row r="540">
@@ -22581,7 +22581,7 @@
         <v>17</v>
       </c>
       <c r="K540" t="n">
-        <v>2.870154078329892</v>
+        <v>2.866706334414398</v>
       </c>
     </row>
     <row r="541">
@@ -22622,7 +22622,7 @@
         <v>17</v>
       </c>
       <c r="K541" t="n">
-        <v>2.870154078329892</v>
+        <v>2.866706334414398</v>
       </c>
     </row>
     <row r="542">
@@ -22663,7 +22663,7 @@
         <v>17</v>
       </c>
       <c r="K542" t="n">
-        <v>2.865640892468579</v>
+        <v>2.865494459446364</v>
       </c>
     </row>
     <row r="543">
@@ -22704,7 +22704,7 @@
         <v>17</v>
       </c>
       <c r="K543" t="n">
-        <v>2.844243971625958</v>
+        <v>2.845692282925172</v>
       </c>
     </row>
     <row r="544">
@@ -22745,7 +22745,7 @@
         <v>17</v>
       </c>
       <c r="K544" t="n">
-        <v>2.844243971625958</v>
+        <v>2.783374247117243</v>
       </c>
     </row>
     <row r="545">
@@ -22786,7 +22786,7 @@
         <v>17</v>
       </c>
       <c r="K545" t="n">
-        <v>2.717807836364531</v>
+        <v>2.722720924525682</v>
       </c>
     </row>
     <row r="546">
@@ -22827,7 +22827,7 @@
         <v>17</v>
       </c>
       <c r="K546" t="n">
-        <v>2.717807836364531</v>
+        <v>2.722720924525682</v>
       </c>
     </row>
     <row r="547">
@@ -22868,7 +22868,7 @@
         <v>17</v>
       </c>
       <c r="K547" t="n">
-        <v>2.717807836364531</v>
+        <v>2.722720924525682</v>
       </c>
     </row>
     <row r="548">
@@ -22909,7 +22909,7 @@
         <v>17</v>
       </c>
       <c r="K548" t="n">
-        <v>2.684225567178596</v>
+        <v>2.687753595398693</v>
       </c>
     </row>
     <row r="549">
@@ -22950,7 +22950,7 @@
         <v>17</v>
       </c>
       <c r="K549" t="n">
-        <v>2.630079757976199</v>
+        <v>2.637675623147084</v>
       </c>
     </row>
     <row r="550">
@@ -22991,7 +22991,7 @@
         <v>17</v>
       </c>
       <c r="K550" t="n">
-        <v>2.427581805054318</v>
+        <v>2.439177904956317</v>
       </c>
     </row>
     <row r="551">
@@ -23032,7 +23032,7 @@
         <v>17</v>
       </c>
       <c r="K551" t="n">
-        <v>2.334071381730189</v>
+        <v>2.343902136766773</v>
       </c>
     </row>
     <row r="552">
@@ -23073,7 +23073,7 @@
         <v>17</v>
       </c>
       <c r="K552" t="n">
-        <v>2.238776008191027</v>
+        <v>2.248596866274625</v>
       </c>
     </row>
     <row r="553">
@@ -23114,7 +23114,7 @@
         <v>17</v>
       </c>
       <c r="K553" t="n">
-        <v>2.238776008191027</v>
+        <v>2.248596866274625</v>
       </c>
     </row>
     <row r="554">
@@ -23155,7 +23155,7 @@
         <v>17</v>
       </c>
       <c r="K554" t="n">
-        <v>2.144579047588716</v>
+        <v>2.154935973844504</v>
       </c>
     </row>
     <row r="555">
@@ -23196,7 +23196,7 @@
         <v>17</v>
       </c>
       <c r="K555" t="n">
-        <v>2.038847860210264</v>
+        <v>2.049381837453615</v>
       </c>
     </row>
     <row r="556">
@@ -23237,7 +23237,7 @@
         <v>17</v>
       </c>
       <c r="K556" t="n">
-        <v>2.038847860210264</v>
+        <v>2.049381837453615</v>
       </c>
     </row>
     <row r="557">
@@ -23278,7 +23278,7 @@
         <v>17</v>
       </c>
       <c r="K557" t="n">
-        <v>1.856201879555155</v>
+        <v>1.859133763865014</v>
       </c>
     </row>
     <row r="558">
@@ -23319,7 +23319,7 @@
         <v>17</v>
       </c>
       <c r="K558" t="n">
-        <v>1.817567554088942</v>
+        <v>1.820677285763675</v>
       </c>
     </row>
     <row r="559">
@@ -23360,7 +23360,7 @@
         <v>17</v>
       </c>
       <c r="K559" t="n">
-        <v>1.817567554088942</v>
+        <v>1.820677285763675</v>
       </c>
     </row>
     <row r="560">
@@ -23401,7 +23401,7 @@
         <v>17</v>
       </c>
       <c r="K560" t="n">
-        <v>1.817567554088942</v>
+        <v>1.820677285763675</v>
       </c>
     </row>
     <row r="561">
@@ -23442,7 +23442,7 @@
         <v>17</v>
       </c>
       <c r="K561" t="n">
-        <v>1.746901942433143</v>
+        <v>1.748185435513463</v>
       </c>
     </row>
     <row r="562">
@@ -23483,7 +23483,7 @@
         <v>17</v>
       </c>
       <c r="K562" t="n">
-        <v>1.746901942433143</v>
+        <v>1.748185435513463</v>
       </c>
     </row>
     <row r="563">
@@ -23524,7 +23524,7 @@
         <v>17</v>
       </c>
       <c r="K563" t="n">
-        <v>1.742184362518785</v>
+        <v>1.740196313279285</v>
       </c>
     </row>
     <row r="564">
@@ -23565,7 +23565,7 @@
         <v>17</v>
       </c>
       <c r="K564" t="n">
-        <v>1.745410104252429</v>
+        <v>1.743723042002268</v>
       </c>
     </row>
     <row r="565">
@@ -23606,7 +23606,7 @@
         <v>17</v>
       </c>
       <c r="K565" t="n">
-        <v>1.745410104252429</v>
+        <v>1.743723042002268</v>
       </c>
     </row>
     <row r="566">
@@ -23647,7 +23647,7 @@
         <v>17</v>
       </c>
       <c r="K566" t="n">
-        <v>1.745410104252429</v>
+        <v>1.743723042002268</v>
       </c>
     </row>
     <row r="567">
@@ -23688,7 +23688,7 @@
         <v>17</v>
       </c>
       <c r="K567" t="n">
-        <v>1.809728146976141</v>
+        <v>1.807950483578256</v>
       </c>
     </row>
     <row r="568">
@@ -23729,7 +23729,7 @@
         <v>17</v>
       </c>
       <c r="K568" t="n">
-        <v>1.835715716574616</v>
+        <v>1.859542666348718</v>
       </c>
     </row>
     <row r="569">
@@ -23770,7 +23770,7 @@
         <v>17</v>
       </c>
       <c r="K569" t="n">
-        <v>1.862036901681544</v>
+        <v>1.886987426163684</v>
       </c>
     </row>
     <row r="570">
@@ -23811,7 +23811,7 @@
         <v>17</v>
       </c>
       <c r="K570" t="n">
-        <v>1.962326893820399</v>
+        <v>1.959659445840087</v>
       </c>
     </row>
     <row r="571">
@@ -23852,7 +23852,7 @@
         <v>17</v>
       </c>
       <c r="K571" t="n">
-        <v>1.980580078530179</v>
+        <v>1.979231130357909</v>
       </c>
     </row>
     <row r="572">
@@ -23893,7 +23893,7 @@
         <v>17</v>
       </c>
       <c r="K572" t="n">
-        <v>1.980580078530179</v>
+        <v>1.990955247465537</v>
       </c>
     </row>
     <row r="573">
@@ -23934,7 +23934,7 @@
         <v>17</v>
       </c>
       <c r="K573" t="n">
-        <v>2.004081183329462</v>
+        <v>2.004413207121422</v>
       </c>
     </row>
     <row r="574">
@@ -23975,7 +23975,7 @@
         <v>17</v>
       </c>
       <c r="K574" t="n">
-        <v>2.004081183329462</v>
+        <v>2.004413207121422</v>
       </c>
     </row>
     <row r="575">
@@ -24016,7 +24016,7 @@
         <v>17</v>
       </c>
       <c r="K575" t="n">
-        <v>2.004081183329462</v>
+        <v>1.997765958939419</v>
       </c>
     </row>
     <row r="576">
@@ -24057,7 +24057,7 @@
         <v>17</v>
       </c>
       <c r="K576" t="n">
-        <v>1.996924372598213</v>
+        <v>1.993690697915959</v>
       </c>
     </row>
     <row r="577">
@@ -24098,7 +24098,7 @@
         <v>17</v>
       </c>
       <c r="K577" t="n">
-        <v>1.986950331464383</v>
+        <v>1.988577904732337</v>
       </c>
     </row>
     <row r="578">
@@ -24139,7 +24139,7 @@
         <v>17</v>
       </c>
       <c r="K578" t="n">
-        <v>1.986950331464383</v>
+        <v>1.988577904732337</v>
       </c>
     </row>
     <row r="579">
@@ -24180,7 +24180,7 @@
         <v>17</v>
       </c>
       <c r="K579" t="n">
-        <v>1.956046651482979</v>
+        <v>1.959973737944898</v>
       </c>
     </row>
     <row r="580">
@@ -24221,7 +24221,7 @@
         <v>17</v>
       </c>
       <c r="K580" t="n">
-        <v>1.956046651482979</v>
+        <v>1.959973737944898</v>
       </c>
     </row>
     <row r="581">
@@ -24262,7 +24262,7 @@
         <v>17</v>
       </c>
       <c r="K581" t="n">
-        <v>1.956046651482979</v>
+        <v>1.959973737944898</v>
       </c>
     </row>
     <row r="582">
@@ -24303,7 +24303,7 @@
         <v>17</v>
       </c>
       <c r="K582" t="n">
-        <v>1.845370682992889</v>
+        <v>1.852351311404467</v>
       </c>
     </row>
     <row r="583">
@@ -24344,7 +24344,7 @@
         <v>17</v>
       </c>
       <c r="K583" t="n">
-        <v>1.845370682992889</v>
+        <v>1.852351311404467</v>
       </c>
     </row>
     <row r="584">
@@ -24385,7 +24385,7 @@
         <v>17</v>
       </c>
       <c r="K584" t="n">
-        <v>1.734479886124699</v>
+        <v>1.706173922794871</v>
       </c>
     </row>
     <row r="585">
@@ -24426,7 +24426,7 @@
         <v>17</v>
       </c>
       <c r="K585" t="n">
-        <v>1.660404835828053</v>
+        <v>1.662273983214669</v>
       </c>
     </row>
     <row r="586">
@@ -24467,7 +24467,7 @@
         <v>17</v>
       </c>
       <c r="K586" t="n">
-        <v>1.641039111412354</v>
+        <v>1.643343736095451</v>
       </c>
     </row>
     <row r="587">
@@ -24508,7 +24508,7 @@
         <v>17</v>
       </c>
       <c r="K587" t="n">
-        <v>1.611700773579681</v>
+        <v>1.615536879555169</v>
       </c>
     </row>
     <row r="588">
@@ -24549,7 +24549,7 @@
         <v>17</v>
       </c>
       <c r="K588" t="n">
-        <v>1.492208586146571</v>
+        <v>1.491800404154799</v>
       </c>
     </row>
     <row r="589">
@@ -24590,7 +24590,7 @@
         <v>17</v>
       </c>
       <c r="K589" t="n">
-        <v>1.494100148011802</v>
+        <v>1.493646893409386</v>
       </c>
     </row>
     <row r="590">
@@ -24631,7 +24631,7 @@
         <v>17</v>
       </c>
       <c r="K590" t="n">
-        <v>1.487764473312807</v>
+        <v>1.489345441382372</v>
       </c>
     </row>
     <row r="591">
@@ -24672,7 +24672,7 @@
         <v>17</v>
       </c>
       <c r="K591" t="n">
-        <v>1.345432206117254</v>
+        <v>1.350677572188717</v>
       </c>
     </row>
     <row r="592">
@@ -24713,7 +24713,7 @@
         <v>17</v>
       </c>
       <c r="K592" t="n">
-        <v>1.303125184564244</v>
+        <v>1.306530915824913</v>
       </c>
     </row>
     <row r="593">
@@ -24754,7 +24754,7 @@
         <v>17</v>
       </c>
       <c r="K593" t="n">
-        <v>1.303125184564244</v>
+        <v>1.306530915824913</v>
       </c>
     </row>
     <row r="594">
@@ -24795,7 +24795,7 @@
         <v>17</v>
       </c>
       <c r="K594" t="n">
-        <v>1.303125184564244</v>
+        <v>1.306530915824913</v>
       </c>
     </row>
     <row r="595">
@@ -24836,7 +24836,7 @@
         <v>17</v>
       </c>
       <c r="K595" t="n">
-        <v>1.281008194234858</v>
+        <v>1.279551924590051</v>
       </c>
     </row>
     <row r="596">
@@ -24877,7 +24877,7 @@
         <v>17</v>
       </c>
       <c r="K596" t="n">
-        <v>1.281008194234858</v>
+        <v>1.279551924590051</v>
       </c>
     </row>
     <row r="597">
@@ -24918,7 +24918,7 @@
         <v>17</v>
       </c>
       <c r="K597" t="n">
-        <v>1.2859552953439</v>
+        <v>1.286362999645952</v>
       </c>
     </row>
     <row r="598">
@@ -24959,7 +24959,7 @@
         <v>17</v>
       </c>
       <c r="K598" t="n">
-        <v>1.274415387865985</v>
+        <v>1.274101588371236</v>
       </c>
     </row>
     <row r="599">
@@ -25000,7 +25000,7 @@
         <v>17</v>
       </c>
       <c r="K599" t="n">
-        <v>1.274415387865985</v>
+        <v>1.274101588371236</v>
       </c>
     </row>
     <row r="600">
@@ -25041,7 +25041,7 @@
         <v>17</v>
       </c>
       <c r="K600" t="n">
-        <v>1.260082482549641</v>
+        <v>1.259867536598453</v>
       </c>
     </row>
     <row r="601">
@@ -25082,7 +25082,7 @@
         <v>17</v>
       </c>
       <c r="K601" t="n">
-        <v>1.260082482549641</v>
+        <v>1.259867536598453</v>
       </c>
     </row>
     <row r="602">
@@ -25123,7 +25123,7 @@
         <v>17</v>
       </c>
       <c r="K602" t="n">
-        <v>1.266382654614123</v>
+        <v>1.26522043998589</v>
       </c>
     </row>
     <row r="603">
@@ -25164,7 +25164,7 @@
         <v>17</v>
       </c>
       <c r="K603" t="n">
-        <v>1.282892726058394</v>
+        <v>1.280825302376456</v>
       </c>
     </row>
     <row r="604">
@@ -25205,7 +25205,7 @@
         <v>17</v>
       </c>
       <c r="K604" t="n">
-        <v>1.30853353375019</v>
+        <v>1.306061398399978</v>
       </c>
     </row>
     <row r="605">
@@ -25246,7 +25246,7 @@
         <v>17</v>
       </c>
       <c r="K605" t="n">
-        <v>1.327391194221972</v>
+        <v>1.326214107332671</v>
       </c>
     </row>
     <row r="606">
@@ -25287,7 +25287,7 @@
         <v>17</v>
       </c>
       <c r="K606" t="n">
-        <v>1.346059557871007</v>
+        <v>1.344929048250361</v>
       </c>
     </row>
     <row r="607">
@@ -25328,7 +25328,7 @@
         <v>17</v>
       </c>
       <c r="K607" t="n">
-        <v>1.356322692107975</v>
+        <v>1.354925506824928</v>
       </c>
     </row>
     <row r="608">
@@ -25369,7 +25369,7 @@
         <v>17</v>
       </c>
       <c r="K608" t="n">
-        <v>1.420690940484201</v>
+        <v>1.417389977406472</v>
       </c>
     </row>
     <row r="609">
@@ -25410,7 +25410,7 @@
         <v>17</v>
       </c>
       <c r="K609" t="n">
-        <v>1.527860208659813</v>
+        <v>1.524853285746458</v>
       </c>
     </row>
     <row r="610">
@@ -25451,7 +25451,7 @@
         <v>17</v>
       </c>
       <c r="K610" t="n">
-        <v>1.667167353380887</v>
+        <v>1.663519348475456</v>
       </c>
     </row>
     <row r="611">
@@ -25492,7 +25492,7 @@
         <v>17</v>
       </c>
       <c r="K611" t="n">
-        <v>1.667167353380887</v>
+        <v>1.663519348475456</v>
       </c>
     </row>
     <row r="612">
@@ -25533,7 +25533,7 @@
         <v>17</v>
       </c>
       <c r="K612" t="n">
-        <v>1.650024250146939</v>
+        <v>1.65423936606231</v>
       </c>
     </row>
     <row r="613">
@@ -25574,7 +25574,7 @@
         <v>17</v>
       </c>
       <c r="K613" t="n">
-        <v>1.650024250146939</v>
+        <v>1.65423936606231</v>
       </c>
     </row>
     <row r="614">
@@ -25615,7 +25615,7 @@
         <v>17</v>
       </c>
       <c r="K614" t="n">
-        <v>1.534186171939178</v>
+        <v>1.5397257504976</v>
       </c>
     </row>
     <row r="615">
@@ -25656,7 +25656,7 @@
         <v>17</v>
       </c>
       <c r="K615" t="n">
-        <v>1.534186171939178</v>
+        <v>1.5397257504976</v>
       </c>
     </row>
     <row r="616">
@@ -25697,7 +25697,7 @@
         <v>17</v>
       </c>
       <c r="K616" t="n">
-        <v>1.482005634647385</v>
+        <v>1.486343910111528</v>
       </c>
     </row>
     <row r="617">
@@ -25738,7 +25738,7 @@
         <v>17</v>
       </c>
       <c r="K617" t="n">
-        <v>1.482005634647385</v>
+        <v>1.486343910111528</v>
       </c>
     </row>
     <row r="618">
@@ -25779,7 +25779,7 @@
         <v>17</v>
       </c>
       <c r="K618" t="n">
-        <v>1.399767778631465</v>
+        <v>1.401703913724815</v>
       </c>
     </row>
     <row r="619">
@@ -25820,7 +25820,7 @@
         <v>17</v>
       </c>
       <c r="K619" t="n">
-        <v>1.353905726055582</v>
+        <v>1.355811630499738</v>
       </c>
     </row>
     <row r="620">
@@ -25861,7 +25861,7 @@
         <v>17</v>
       </c>
       <c r="K620" t="n">
-        <v>1.331018235521094</v>
+        <v>1.33198131445346</v>
       </c>
     </row>
     <row r="621">
@@ -25902,7 +25902,7 @@
         <v>17</v>
       </c>
       <c r="K621" t="n">
-        <v>1.331018235521094</v>
+        <v>1.33198131445346</v>
       </c>
     </row>
     <row r="622">
@@ -25943,7 +25943,7 @@
         <v>17</v>
       </c>
       <c r="K622" t="n">
-        <v>1.298383147644595</v>
+        <v>1.299252140382469</v>
       </c>
     </row>
     <row r="623">
@@ -25984,7 +25984,7 @@
         <v>17</v>
       </c>
       <c r="K623" t="n">
-        <v>1.298383147644595</v>
+        <v>1.299252140382469</v>
       </c>
     </row>
     <row r="624">
@@ -26025,7 +26025,7 @@
         <v>17</v>
       </c>
       <c r="K624" t="n">
-        <v>1.295642352826704</v>
+        <v>1.296099912946404</v>
       </c>
     </row>
     <row r="625">
@@ -26066,7 +26066,7 @@
         <v>17</v>
       </c>
       <c r="K625" t="n">
-        <v>1.302507533824628</v>
+        <v>1.301008238547854</v>
       </c>
     </row>
     <row r="626">
@@ -26107,7 +26107,7 @@
         <v>17</v>
       </c>
       <c r="K626" t="n">
-        <v>1.30521819885993</v>
+        <v>1.304391633517019</v>
       </c>
     </row>
     <row r="627">
@@ -26148,7 +26148,7 @@
         <v>17</v>
       </c>
       <c r="K627" t="n">
-        <v>1.30521819885993</v>
+        <v>1.304391633517019</v>
       </c>
     </row>
     <row r="628">
@@ -26189,7 +26189,7 @@
         <v>17</v>
       </c>
       <c r="K628" t="n">
-        <v>1.305719822199354</v>
+        <v>1.305990172315368</v>
       </c>
     </row>
     <row r="629">
@@ -26230,7 +26230,7 @@
         <v>17</v>
       </c>
       <c r="K629" t="n">
-        <v>1.305719822199354</v>
+        <v>1.305990172315368</v>
       </c>
     </row>
     <row r="630">
@@ -26271,7 +26271,7 @@
         <v>17</v>
       </c>
       <c r="K630" t="n">
-        <v>1.305719822199354</v>
+        <v>1.305990172315368</v>
       </c>
     </row>
     <row r="631">
@@ -26312,7 +26312,7 @@
         <v>17</v>
       </c>
       <c r="K631" t="n">
-        <v>1.29368426072966</v>
+        <v>1.291159987285746</v>
       </c>
     </row>
     <row r="632">
@@ -26353,7 +26353,7 @@
         <v>17</v>
       </c>
       <c r="K632" t="n">
-        <v>1.260084517704088</v>
+        <v>1.256330931983916</v>
       </c>
     </row>
     <row r="633">
@@ -26394,7 +26394,7 @@
         <v>17</v>
       </c>
       <c r="K633" t="n">
-        <v>1.260084517704088</v>
+        <v>1.215189272189719</v>
       </c>
     </row>
     <row r="634">
@@ -26435,7 +26435,7 @@
         <v>17</v>
       </c>
       <c r="K634" t="n">
-        <v>1.213297095223478</v>
+        <v>1.16419278237956</v>
       </c>
     </row>
     <row r="635">
@@ -26476,7 +26476,7 @@
         <v>17</v>
       </c>
       <c r="K635" t="n">
-        <v>1.213297095223478</v>
+        <v>1.16419278237956</v>
       </c>
     </row>
     <row r="636">
@@ -26517,7 +26517,7 @@
         <v>17</v>
       </c>
       <c r="K636" t="n">
-        <v>1.125014199508566</v>
+        <v>1.121877790431538</v>
       </c>
     </row>
     <row r="637">
@@ -26558,7 +26558,7 @@
         <v>17</v>
       </c>
       <c r="K637" t="n">
-        <v>1.078390558950061</v>
+        <v>1.079986480978993</v>
       </c>
     </row>
     <row r="638">
@@ -26599,7 +26599,7 @@
         <v>17</v>
       </c>
       <c r="K638" t="n">
-        <v>0.7134712381120591</v>
+        <v>0.7163200886780797</v>
       </c>
     </row>
     <row r="639">
@@ -26640,7 +26640,7 @@
         <v>17</v>
       </c>
       <c r="K639" t="n">
-        <v>0.7134712381120591</v>
+        <v>0.7163200886780797</v>
       </c>
     </row>
     <row r="640">
@@ -26681,7 +26681,7 @@
         <v>17</v>
       </c>
       <c r="K640" t="n">
-        <v>0.6507648228686723</v>
+        <v>0.6516415049346538</v>
       </c>
     </row>
     <row r="641">
@@ -26722,7 +26722,7 @@
         <v>17</v>
       </c>
       <c r="K641" t="n">
-        <v>0.6507648228686723</v>
+        <v>0.6516415049346538</v>
       </c>
     </row>
     <row r="642">
@@ -26763,7 +26763,7 @@
         <v>17</v>
       </c>
       <c r="K642" t="n">
-        <v>0.5924652508724821</v>
+        <v>0.5925473862915794</v>
       </c>
     </row>
     <row r="643">
@@ -26804,7 +26804,7 @@
         <v>17</v>
       </c>
       <c r="K643" t="n">
-        <v>0.5996005991178998</v>
+        <v>0.5986412308439157</v>
       </c>
     </row>
     <row r="644">
@@ -26845,7 +26845,7 @@
         <v>17</v>
       </c>
       <c r="K644" t="n">
-        <v>0.9462064831682486</v>
+        <v>0.9417195207792749</v>
       </c>
     </row>
     <row r="645">
@@ -26886,7 +26886,7 @@
         <v>17</v>
       </c>
       <c r="K645" t="n">
-        <v>0.9462064831682486</v>
+        <v>0.9417195207792749</v>
       </c>
     </row>
     <row r="646">
@@ -26927,7 +26927,7 @@
         <v>17</v>
       </c>
       <c r="K646" t="n">
-        <v>1.63474565604999</v>
+        <v>1.628985775806377</v>
       </c>
     </row>
     <row r="647">
@@ -26968,7 +26968,7 @@
         <v>17</v>
       </c>
       <c r="K647" t="n">
-        <v>1.795209020532105</v>
+        <v>1.790881315202244</v>
       </c>
     </row>
     <row r="648">
@@ -27009,7 +27009,7 @@
         <v>17</v>
       </c>
       <c r="K648" t="n">
-        <v>1.97297398788607</v>
+        <v>1.971190475428972</v>
       </c>
     </row>
     <row r="649">
@@ -27050,7 +27050,7 @@
         <v>17</v>
       </c>
       <c r="K649" t="n">
-        <v>1.97297398788607</v>
+        <v>1.971190475428972</v>
       </c>
     </row>
     <row r="650">
@@ -27091,7 +27091,7 @@
         <v>17</v>
       </c>
       <c r="K650" t="n">
-        <v>2.032379599948654</v>
+        <v>2.031767246033111</v>
       </c>
     </row>
     <row r="651">
@@ -27132,7 +27132,7 @@
         <v>17</v>
       </c>
       <c r="K651" t="n">
-        <v>2.041753194816113</v>
+        <v>2.041574565968009</v>
       </c>
     </row>
     <row r="652">
@@ -27173,7 +27173,7 @@
         <v>17</v>
       </c>
       <c r="K652" t="n">
-        <v>2.060565086674625</v>
+        <v>2.059917921005884</v>
       </c>
     </row>
     <row r="653">
@@ -27214,7 +27214,7 @@
         <v>17</v>
       </c>
       <c r="K653" t="n">
-        <v>2.060565086674625</v>
+        <v>2.059917921005884</v>
       </c>
     </row>
     <row r="654">
@@ -27255,7 +27255,7 @@
         <v>17</v>
       </c>
       <c r="K654" t="n">
-        <v>2.060648900898679</v>
+        <v>2.061303390309408</v>
       </c>
     </row>
     <row r="655">
@@ -27296,7 +27296,7 @@
         <v>17</v>
       </c>
       <c r="K655" t="n">
-        <v>2.060648900898679</v>
+        <v>2.036014111490784</v>
       </c>
     </row>
     <row r="656">
@@ -27337,7 +27337,7 @@
         <v>17</v>
       </c>
       <c r="K656" t="n">
-        <v>2.03497563545825</v>
+        <v>2.036014111490784</v>
       </c>
     </row>
     <row r="657">
@@ -27378,7 +27378,7 @@
         <v>17</v>
       </c>
       <c r="K657" t="n">
-        <v>2.000095103024795</v>
+        <v>2.001245795440158</v>
       </c>
     </row>
     <row r="658">
@@ -27419,7 +27419,7 @@
         <v>17</v>
       </c>
       <c r="K658" t="n">
-        <v>2.000095103024795</v>
+        <v>2.001245795440158</v>
       </c>
     </row>
     <row r="659">
@@ -27460,7 +27460,7 @@
         <v>17</v>
       </c>
       <c r="K659" t="n">
-        <v>1.899665170197415</v>
+        <v>1.900011101243681</v>
       </c>
     </row>
     <row r="660">
@@ -27501,7 +27501,7 @@
         <v>17</v>
       </c>
       <c r="K660" t="n">
-        <v>1.892449759396242</v>
+        <v>1.892645869696258</v>
       </c>
     </row>
     <row r="661">
@@ -27542,7 +27542,7 @@
         <v>17</v>
       </c>
       <c r="K661" t="n">
-        <v>1.892449759396242</v>
+        <v>1.897711258687551</v>
       </c>
     </row>
     <row r="662">
@@ -27583,7 +27583,7 @@
         <v>17</v>
       </c>
       <c r="K662" t="n">
-        <v>1.921659565000897</v>
+        <v>1.920886692633361</v>
       </c>
     </row>
     <row r="663">
@@ -27624,7 +27624,7 @@
         <v>17</v>
       </c>
       <c r="K663" t="n">
-        <v>1.903931161355199</v>
+        <v>1.90536347755512</v>
       </c>
     </row>
     <row r="664">
@@ -27665,7 +27665,7 @@
         <v>17</v>
       </c>
       <c r="K664" t="n">
-        <v>1.853426909715054</v>
+        <v>1.855310073539209</v>
       </c>
     </row>
     <row r="665">
@@ -27706,7 +27706,7 @@
         <v>17</v>
       </c>
       <c r="K665" t="n">
-        <v>1.729244602908072</v>
+        <v>1.731378525307109</v>
       </c>
     </row>
     <row r="666">
@@ -27747,7 +27747,7 @@
         <v>17</v>
       </c>
       <c r="K666" t="n">
-        <v>1.663858206516398</v>
+        <v>1.665916897687207</v>
       </c>
     </row>
     <row r="667">
@@ -27788,7 +27788,7 @@
         <v>17</v>
       </c>
       <c r="K667" t="n">
-        <v>1.600235082546183</v>
+        <v>1.602356794947145</v>
       </c>
     </row>
     <row r="668">
@@ -27829,7 +27829,7 @@
         <v>17</v>
       </c>
       <c r="K668" t="n">
-        <v>1.47142669386343</v>
+        <v>1.470702534117862</v>
       </c>
     </row>
     <row r="669">
@@ -27870,7 +27870,7 @@
         <v>17</v>
       </c>
       <c r="K669" t="n">
-        <v>1.47142669386343</v>
+        <v>1.470702534117862</v>
       </c>
     </row>
     <row r="670">
@@ -27911,7 +27911,7 @@
         <v>17</v>
       </c>
       <c r="K670" t="n">
-        <v>1.538906087956075</v>
+        <v>1.537474839854096</v>
       </c>
     </row>
     <row r="671">
@@ -27952,7 +27952,7 @@
         <v>17</v>
       </c>
       <c r="K671" t="n">
-        <v>1.703508383683169</v>
+        <v>1.702157284105538</v>
       </c>
     </row>
     <row r="672">
@@ -27993,7 +27993,7 @@
         <v>17</v>
       </c>
       <c r="K672" t="n">
-        <v>1.703508383683169</v>
+        <v>1.702157284105538</v>
       </c>
     </row>
     <row r="673">
@@ -28034,7 +28034,7 @@
         <v>17</v>
       </c>
       <c r="K673" t="n">
-        <v>1.715112175177647</v>
+        <v>1.715555737046316</v>
       </c>
     </row>
     <row r="674">
@@ -28075,7 +28075,7 @@
         <v>17</v>
       </c>
       <c r="K674" t="n">
-        <v>1.652387744370913</v>
+        <v>1.652231919016752</v>
       </c>
     </row>
     <row r="675">
@@ -28116,7 +28116,7 @@
         <v>17</v>
       </c>
       <c r="K675" t="n">
-        <v>1.603989313445332</v>
+        <v>1.605027004382599</v>
       </c>
     </row>
     <row r="676">
@@ -28157,7 +28157,7 @@
         <v>17</v>
       </c>
       <c r="K676" t="n">
-        <v>1.603989313445332</v>
+        <v>1.605027004382599</v>
       </c>
     </row>
     <row r="677">
@@ -28198,7 +28198,7 @@
         <v>17</v>
       </c>
       <c r="K677" t="n">
-        <v>1.577903908214789</v>
+        <v>1.579389464468934</v>
       </c>
     </row>
     <row r="678">
@@ -28239,7 +28239,7 @@
         <v>17</v>
       </c>
       <c r="K678" t="n">
-        <v>1.412364445572398</v>
+        <v>1.413282027522598</v>
       </c>
     </row>
     <row r="679">
@@ -28280,7 +28280,7 @@
         <v>17</v>
       </c>
       <c r="K679" t="n">
-        <v>1.412364445572398</v>
+        <v>1.413282027522598</v>
       </c>
     </row>
     <row r="680">
@@ -28321,7 +28321,7 @@
         <v>17</v>
       </c>
       <c r="K680" t="n">
-        <v>1.399882724077136</v>
+        <v>1.40003595283167</v>
       </c>
     </row>
     <row r="681">
@@ -28362,7 +28362,7 @@
         <v>17</v>
       </c>
       <c r="K681" t="n">
-        <v>1.71110683019375</v>
+        <v>1.709396705923041</v>
       </c>
     </row>
     <row r="682">
@@ -28403,7 +28403,7 @@
         <v>17</v>
       </c>
       <c r="K682" t="n">
-        <v>1.769412323809633</v>
+        <v>1.768812659028195</v>
       </c>
     </row>
     <row r="683">
@@ -28444,7 +28444,7 @@
         <v>17</v>
       </c>
       <c r="K683" t="n">
-        <v>1.781238696307794</v>
+        <v>1.780650728842499</v>
       </c>
     </row>
     <row r="684">
@@ -28485,7 +28485,7 @@
         <v>17</v>
       </c>
       <c r="K684" t="n">
-        <v>1.783355030596451</v>
+        <v>1.783542269114979</v>
       </c>
     </row>
     <row r="685">
@@ -28526,7 +28526,7 @@
         <v>17</v>
       </c>
       <c r="K685" t="n">
-        <v>1.780960895197733</v>
+        <v>1.780535765316901</v>
       </c>
     </row>
     <row r="686">
@@ -28567,7 +28567,7 @@
         <v>17</v>
       </c>
       <c r="K686" t="n">
-        <v>1.755440695630795</v>
+        <v>1.756560674501993</v>
       </c>
     </row>
     <row r="687">
@@ -28608,7 +28608,7 @@
         <v>17</v>
       </c>
       <c r="K687" t="n">
-        <v>1.785086715737576</v>
+        <v>1.783848030992434</v>
       </c>
     </row>
     <row r="688">
@@ -28649,7 +28649,7 @@
         <v>17</v>
       </c>
       <c r="K688" t="n">
-        <v>1.912532105199414</v>
+        <v>1.910137514771619</v>
       </c>
     </row>
     <row r="689">
@@ -28690,7 +28690,7 @@
         <v>17</v>
       </c>
       <c r="K689" t="n">
-        <v>1.969030379816437</v>
+        <v>1.967574134754464</v>
       </c>
     </row>
     <row r="690">
@@ -28731,7 +28731,7 @@
         <v>17</v>
       </c>
       <c r="K690" t="n">
-        <v>2.027817075320768</v>
+        <v>2.026268747150074</v>
       </c>
     </row>
     <row r="691">
@@ -28772,7 +28772,7 @@
         <v>17</v>
       </c>
       <c r="K691" t="n">
-        <v>2.14964006974536</v>
+        <v>2.148692733944594</v>
       </c>
     </row>
     <row r="692">
@@ -28813,7 +28813,7 @@
         <v>17</v>
       </c>
       <c r="K692" t="n">
-        <v>2.1784018627318</v>
+        <v>2.177454507840276</v>
       </c>
     </row>
     <row r="693">
@@ -28854,7 +28854,7 @@
         <v>17</v>
       </c>
       <c r="K693" t="n">
-        <v>2.210603256388768</v>
+        <v>2.209455906075132</v>
       </c>
     </row>
     <row r="694">
@@ -28895,7 +28895,7 @@
         <v>17</v>
       </c>
       <c r="K694" t="n">
-        <v>2.241294531808451</v>
+        <v>2.241315683544716</v>
       </c>
     </row>
     <row r="695">
@@ -28936,7 +28936,7 @@
         <v>17</v>
       </c>
       <c r="K695" t="n">
-        <v>2.232676816381428</v>
+        <v>2.233251038286631</v>
       </c>
     </row>
     <row r="696">
@@ -28977,7 +28977,7 @@
         <v>17</v>
       </c>
       <c r="K696" t="n">
-        <v>2.232676816381428</v>
+        <v>2.233251038286631</v>
       </c>
     </row>
     <row r="697">
@@ -29018,7 +29018,7 @@
         <v>17</v>
       </c>
       <c r="K697" t="n">
-        <v>2.204917273889099</v>
+        <v>2.206071736624143</v>
       </c>
     </row>
     <row r="698">
@@ -29059,7 +29059,7 @@
         <v>17</v>
       </c>
       <c r="K698" t="n">
-        <v>2.176257389896063</v>
+        <v>2.175589172523468</v>
       </c>
     </row>
     <row r="699">
@@ -29100,7 +29100,7 @@
         <v>17</v>
       </c>
       <c r="K699" t="n">
-        <v>2.201530218012264</v>
+        <v>2.200555925412428</v>
       </c>
     </row>
     <row r="700">
@@ -29141,7 +29141,7 @@
         <v>17</v>
       </c>
       <c r="K700" t="n">
-        <v>2.23868717361171</v>
+        <v>2.237504725845703</v>
       </c>
     </row>
     <row r="701">
@@ -29182,7 +29182,7 @@
         <v>17</v>
       </c>
       <c r="K701" t="n">
-        <v>2.309774118534807</v>
+        <v>2.308879551575882</v>
       </c>
     </row>
     <row r="702">
@@ -29223,7 +29223,7 @@
         <v>17</v>
       </c>
       <c r="K702" t="n">
-        <v>2.388092601364097</v>
+        <v>2.386997265371564</v>
       </c>
     </row>
     <row r="703">
@@ -29264,7 +29264,7 @@
         <v>17</v>
       </c>
       <c r="K703" t="n">
-        <v>2.465718934383256</v>
+        <v>2.464569621503041</v>
       </c>
     </row>
     <row r="704">
@@ -29305,7 +29305,7 @@
         <v>17</v>
       </c>
       <c r="K704" t="n">
-        <v>2.490136085326713</v>
+        <v>2.490729208894227</v>
       </c>
     </row>
     <row r="705">
@@ -29346,7 +29346,7 @@
         <v>17</v>
       </c>
       <c r="K705" t="n">
-        <v>2.490136085326713</v>
+        <v>2.490729208894227</v>
       </c>
     </row>
     <row r="706">
@@ -29387,7 +29387,7 @@
         <v>17</v>
       </c>
       <c r="K706" t="n">
-        <v>2.503113570187197</v>
+        <v>2.504462536992332</v>
       </c>
     </row>
     <row r="707">
@@ -29428,7 +29428,7 @@
         <v>17</v>
       </c>
       <c r="K707" t="n">
-        <v>2.553051190149633</v>
+        <v>2.553397645567701</v>
       </c>
     </row>
     <row r="708">
@@ -29469,7 +29469,7 @@
         <v>17</v>
       </c>
       <c r="K708" t="n">
-        <v>2.553051190149633</v>
+        <v>2.553397645567701</v>
       </c>
     </row>
     <row r="709">
@@ -29510,7 +29510,7 @@
         <v>17</v>
       </c>
       <c r="K709" t="n">
-        <v>2.244130348229967</v>
+        <v>2.247280248291214</v>
       </c>
     </row>
     <row r="710">
@@ -29551,7 +29551,7 @@
         <v>17</v>
       </c>
       <c r="K710" t="n">
-        <v>2.244130348229967</v>
+        <v>2.167083794246012</v>
       </c>
     </row>
     <row r="711">
@@ -29592,7 +29592,7 @@
         <v>17</v>
       </c>
       <c r="K711" t="n">
-        <v>2.136331220697764</v>
+        <v>2.136705446085197</v>
       </c>
     </row>
     <row r="712">
@@ -29633,7 +29633,7 @@
         <v>17</v>
       </c>
       <c r="K712" t="n">
-        <v>2.136331220697764</v>
+        <v>2.136705446085197</v>
       </c>
     </row>
     <row r="713">
@@ -29674,7 +29674,7 @@
         <v>17</v>
       </c>
       <c r="K713" t="n">
-        <v>2.136331220697764</v>
+        <v>2.136705446085197</v>
       </c>
     </row>
     <row r="714">
@@ -29715,7 +29715,7 @@
         <v>17</v>
       </c>
       <c r="K714" t="n">
-        <v>2.433497608595228</v>
+        <v>2.428588151389989</v>
       </c>
     </row>
     <row r="715">
@@ -29756,7 +29756,7 @@
         <v>17</v>
       </c>
       <c r="K715" t="n">
-        <v>2.586831605159269</v>
+        <v>2.582246894953097</v>
       </c>
     </row>
     <row r="716">
@@ -29797,7 +29797,7 @@
         <v>17</v>
       </c>
       <c r="K716" t="n">
-        <v>2.853264179496559</v>
+        <v>2.850566363044912</v>
       </c>
     </row>
     <row r="717">
@@ -29838,7 +29838,7 @@
         <v>17</v>
       </c>
       <c r="K717" t="n">
-        <v>2.948537104422424</v>
+        <v>2.948758862773805</v>
       </c>
     </row>
     <row r="718">
@@ -29879,7 +29879,7 @@
         <v>17</v>
       </c>
       <c r="K718" t="n">
-        <v>2.91800220896181</v>
+        <v>2.919685076368487</v>
       </c>
     </row>
     <row r="719">
@@ -29920,7 +29920,7 @@
         <v>17</v>
       </c>
       <c r="K719" t="n">
-        <v>2.800867818349423</v>
+        <v>2.806247925239674</v>
       </c>
     </row>
     <row r="720">
@@ -29961,7 +29961,7 @@
         <v>17</v>
       </c>
       <c r="K720" t="n">
-        <v>2.521628484939811</v>
+        <v>2.535358130088557</v>
       </c>
     </row>
     <row r="721">
@@ -30002,7 +30002,7 @@
         <v>17</v>
       </c>
       <c r="K721" t="n">
-        <v>2.139153103886682</v>
+        <v>2.146384961911092</v>
       </c>
     </row>
     <row r="722">
@@ -30043,7 +30043,7 @@
         <v>17</v>
       </c>
       <c r="K722" t="n">
-        <v>2.139153103886682</v>
+        <v>2.146384961911092</v>
       </c>
     </row>
     <row r="723">
@@ -30084,7 +30084,7 @@
         <v>17</v>
       </c>
       <c r="K723" t="n">
-        <v>1.550643279421104</v>
+        <v>1.553193377955109</v>
       </c>
     </row>
     <row r="724">
@@ -30125,7 +30125,7 @@
         <v>17</v>
       </c>
       <c r="K724" t="n">
-        <v>1.471232439578365</v>
+        <v>1.473752659697231</v>
       </c>
     </row>
     <row r="725">
@@ -30166,7 +30166,7 @@
         <v>17</v>
       </c>
       <c r="K725" t="n">
-        <v>1.207992850867279</v>
+        <v>1.209621857735668</v>
       </c>
     </row>
     <row r="726">
@@ -30207,7 +30207,7 @@
         <v>17</v>
       </c>
       <c r="K726" t="n">
-        <v>1.207992850867279</v>
+        <v>1.209621857735668</v>
       </c>
     </row>
     <row r="727">
@@ -30248,7 +30248,7 @@
         <v>17</v>
       </c>
       <c r="K727" t="n">
-        <v>1.086634445365576</v>
+        <v>1.087851462499902</v>
       </c>
     </row>
     <row r="728">
@@ -30289,7 +30289,7 @@
         <v>17</v>
       </c>
       <c r="K728" t="n">
-        <v>1.086634445365576</v>
+        <v>1.087851462499902</v>
       </c>
     </row>
     <row r="729">
@@ -30330,7 +30330,7 @@
         <v>17</v>
       </c>
       <c r="K729" t="n">
-        <v>1.048119304831252</v>
+        <v>1.04929791404979</v>
       </c>
     </row>
     <row r="730">
@@ -30371,7 +30371,7 @@
         <v>17</v>
       </c>
       <c r="K730" t="n">
-        <v>1.048119304831252</v>
+        <v>1.04929791404979</v>
       </c>
     </row>
     <row r="731">
@@ -30412,7 +30412,7 @@
         <v>17</v>
       </c>
       <c r="K731" t="n">
-        <v>0.9661067312076271</v>
+        <v>0.966159879585053</v>
       </c>
     </row>
     <row r="732">
@@ -30453,7 +30453,7 @@
         <v>17</v>
       </c>
       <c r="K732" t="n">
-        <v>0.9655947500663812</v>
+        <v>0.9655601765344501</v>
       </c>
     </row>
     <row r="733">
@@ -30494,7 +30494,7 @@
         <v>17</v>
       </c>
       <c r="K733" t="n">
-        <v>0.9775732986569576</v>
+        <v>0.9773161611775558</v>
       </c>
     </row>
     <row r="734">
@@ -30535,7 +30535,7 @@
         <v>17</v>
       </c>
       <c r="K734" t="n">
-        <v>0.9925568689370622</v>
+        <v>0.9927517517659337</v>
       </c>
     </row>
     <row r="735">
@@ -30576,7 +30576,7 @@
         <v>17</v>
       </c>
       <c r="K735" t="n">
-        <v>0.9925568689370622</v>
+        <v>0.9927517517659337</v>
       </c>
     </row>
     <row r="736">
@@ -30617,7 +30617,7 @@
         <v>17</v>
       </c>
       <c r="K736" t="n">
-        <v>0.9518819758606194</v>
+        <v>0.9532379376294584</v>
       </c>
     </row>
     <row r="737">
@@ -30658,7 +30658,7 @@
         <v>17</v>
       </c>
       <c r="K737" t="n">
-        <v>0.9518819758606194</v>
+        <v>0.9532379376294584</v>
       </c>
     </row>
     <row r="738">
@@ -30699,7 +30699,7 @@
         <v>17</v>
       </c>
       <c r="K738" t="n">
-        <v>0.9080643879959365</v>
+        <v>0.9094044677918984</v>
       </c>
     </row>
     <row r="739">
@@ -30740,7 +30740,7 @@
         <v>17</v>
       </c>
       <c r="K739" t="n">
-        <v>0.9080643879959365</v>
+        <v>0.8450853899903358</v>
       </c>
     </row>
     <row r="740">
@@ -30781,7 +30781,7 @@
         <v>17</v>
       </c>
       <c r="K740" t="n">
-        <v>0.8424879422224427</v>
+        <v>0.8450853899903358</v>
       </c>
     </row>
     <row r="741">
@@ -30822,7 +30822,7 @@
         <v>17</v>
       </c>
       <c r="K741" t="n">
-        <v>0.6808004742669662</v>
+        <v>0.6837552297184772</v>
       </c>
     </row>
     <row r="742">
@@ -30863,7 +30863,7 @@
         <v>17</v>
       </c>
       <c r="K742" t="n">
-        <v>0.6808004742669662</v>
+        <v>0.6837552297184772</v>
       </c>
     </row>
     <row r="743">
@@ -30904,7 +30904,7 @@
         <v>17</v>
       </c>
       <c r="K743" t="n">
-        <v>0.4756520454101509</v>
+        <v>0.4764597182819884</v>
       </c>
     </row>
     <row r="744">
@@ -30945,7 +30945,7 @@
         <v>17</v>
       </c>
       <c r="K744" t="n">
-        <v>0.4756520454101509</v>
+        <v>0.4764597182819884</v>
       </c>
     </row>
     <row r="745">
@@ -30986,7 +30986,7 @@
         <v>17</v>
       </c>
       <c r="K745" t="n">
-        <v>0.4117528459966467</v>
+        <v>0.4121737394628424</v>
       </c>
     </row>
     <row r="746">
@@ -31027,7 +31027,7 @@
         <v>17</v>
       </c>
       <c r="K746" t="n">
-        <v>0.3909038649721402</v>
+        <v>0.3912831549217073</v>
       </c>
     </row>
     <row r="747">
@@ -31068,7 +31068,7 @@
         <v>17</v>
       </c>
       <c r="K747" t="n">
-        <v>0.3531253800104767</v>
+        <v>0.353410321237339</v>
       </c>
     </row>
     <row r="748">
@@ -31109,7 +31109,7 @@
         <v>17</v>
       </c>
       <c r="K748" t="n">
-        <v>0.4605004396576108</v>
+        <v>0.4588550018033142</v>
       </c>
     </row>
     <row r="749">
@@ -31150,7 +31150,7 @@
         <v>17</v>
       </c>
       <c r="K749" t="n">
-        <v>0.4605004396576108</v>
+        <v>0.4588550018033142</v>
       </c>
     </row>
     <row r="750">
@@ -31191,7 +31191,7 @@
         <v>17</v>
       </c>
       <c r="K750" t="n">
-        <v>0.747506132454011</v>
+        <v>0.7452489496455939</v>
       </c>
     </row>
     <row r="751">
@@ -31232,7 +31232,7 @@
         <v>17</v>
       </c>
       <c r="K751" t="n">
-        <v>0.747506132454011</v>
+        <v>0.7452489496455939</v>
       </c>
     </row>
     <row r="752">
@@ -31273,7 +31273,7 @@
         <v>17</v>
       </c>
       <c r="K752" t="n">
-        <v>0.8417522948408676</v>
+        <v>0.8399580175346417</v>
       </c>
     </row>
     <row r="753">
@@ -31314,7 +31314,7 @@
         <v>17</v>
       </c>
       <c r="K753" t="n">
-        <v>0.8887031799216143</v>
+        <v>0.889089197296262</v>
       </c>
     </row>
     <row r="754">
@@ -31355,7 +31355,7 @@
         <v>17</v>
       </c>
       <c r="K754" t="n">
-        <v>0.8887031799216143</v>
+        <v>0.889089197296262</v>
       </c>
     </row>
     <row r="755">
@@ -31396,7 +31396,7 @@
         <v>17</v>
       </c>
       <c r="K755" t="n">
-        <v>0.8265063909257685</v>
+        <v>0.8270582124375361</v>
       </c>
     </row>
     <row r="756">
@@ -31437,7 +31437,7 @@
         <v>17</v>
       </c>
       <c r="K756" t="n">
-        <v>0.8121075637217939</v>
+        <v>0.8124117704397437</v>
       </c>
     </row>
     <row r="757">
@@ -31478,7 +31478,7 @@
         <v>17</v>
       </c>
       <c r="K757" t="n">
-        <v>0.8121075637217939</v>
+        <v>0.8124117704397437</v>
       </c>
     </row>
     <row r="758">
@@ -31519,7 +31519,7 @@
         <v>17</v>
       </c>
       <c r="K758" t="n">
-        <v>0.7121848915213498</v>
+        <v>0.712587931174179</v>
       </c>
     </row>
     <row r="759">
@@ -31560,7 +31560,7 @@
         <v>17</v>
       </c>
       <c r="K759" t="n">
-        <v>0.6401989602394428</v>
+        <v>0.6413421637763144</v>
       </c>
     </row>
     <row r="760">
@@ -31601,7 +31601,7 @@
         <v>17</v>
       </c>
       <c r="K760" t="n">
-        <v>0.5839599012598736</v>
+        <v>0.5850636167525555</v>
       </c>
     </row>
     <row r="761">
@@ -31642,7 +31642,7 @@
         <v>17</v>
       </c>
       <c r="K761" t="n">
-        <v>0.4021251760241288</v>
+        <v>0.4029865107203582</v>
       </c>
     </row>
     <row r="762">
@@ -31683,7 +31683,7 @@
         <v>17</v>
       </c>
       <c r="K762" t="n">
-        <v>0.4021251760241288</v>
+        <v>0.4029865107203582</v>
       </c>
     </row>
     <row r="763">
@@ -31724,7 +31724,7 @@
         <v>17</v>
       </c>
       <c r="K763" t="n">
-        <v>0.3328372441266683</v>
+        <v>0.3321723208362844</v>
       </c>
     </row>
     <row r="764">
@@ -31765,7 +31765,7 @@
         <v>17</v>
       </c>
       <c r="K764" t="n">
-        <v>0.3853355438933542</v>
+        <v>0.385281709917049</v>
       </c>
     </row>
     <row r="765">
@@ -31806,7 +31806,7 @@
         <v>17</v>
       </c>
       <c r="K765" t="n">
-        <v>0.4119789275338037</v>
+        <v>0.4128915147187552</v>
       </c>
     </row>
     <row r="766">
@@ -31847,7 +31847,7 @@
         <v>17</v>
       </c>
       <c r="K766" t="n">
-        <v>0.4244121626830977</v>
+        <v>0.4256015005453583</v>
       </c>
     </row>
     <row r="767">
@@ -31888,7 +31888,7 @@
         <v>17</v>
       </c>
       <c r="K767" t="n">
-        <v>0.4368977626424147</v>
+        <v>0.439484970388676</v>
       </c>
     </row>
     <row r="768">
@@ -31929,7 +31929,7 @@
         <v>17</v>
       </c>
       <c r="K768" t="n">
-        <v>0.4368977626424147</v>
+        <v>0.439484970388676</v>
       </c>
     </row>
     <row r="769">
@@ -31970,7 +31970,7 @@
         <v>17</v>
       </c>
       <c r="K769" t="n">
-        <v>0.4368977626424147</v>
+        <v>0.439484970388676</v>
       </c>
     </row>
     <row r="770">
@@ -32011,7 +32011,7 @@
         <v>17</v>
       </c>
       <c r="K770" t="n">
-        <v>0.3283448541635943</v>
+        <v>0.3284160370113161</v>
       </c>
     </row>
     <row r="771">
@@ -32052,7 +32052,7 @@
         <v>17</v>
       </c>
       <c r="K771" t="n">
-        <v>0.3283448541635943</v>
+        <v>0.3284160370113161</v>
       </c>
     </row>
     <row r="772">
@@ -32093,7 +32093,7 @@
         <v>17</v>
       </c>
       <c r="K772" t="n">
-        <v>0.2924343832170521</v>
+        <v>0.2930110602346358</v>
       </c>
     </row>
     <row r="773">
@@ -32134,7 +32134,7 @@
         <v>17</v>
       </c>
       <c r="K773" t="n">
-        <v>0.3731010580823801</v>
+        <v>0.3731580124506089</v>
       </c>
     </row>
     <row r="774">
@@ -32175,7 +32175,7 @@
         <v>17</v>
       </c>
       <c r="K774" t="n">
-        <v>0.4306504635957668</v>
+        <v>0.4306595931450363</v>
       </c>
     </row>
     <row r="775">
@@ -32216,7 +32216,7 @@
         <v>17</v>
       </c>
       <c r="K775" t="n">
-        <v>0.4891842979695386</v>
+        <v>0.4892022975808537</v>
       </c>
     </row>
     <row r="776">
@@ -32257,7 +32257,7 @@
         <v>17</v>
       </c>
       <c r="K776" t="n">
-        <v>0.4891842979695386</v>
+        <v>0.4892022975808537</v>
       </c>
     </row>
     <row r="777">
